--- a/automation/reports/Excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Passed_Test_Cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="617">
   <si>
     <t>Test ID</t>
   </si>
@@ -143,39 +143,6 @@
     <t>Validate Profile Management scenario 15</t>
   </si>
   <si>
-    <t>TC_RUI_001</t>
-  </si>
-  <si>
-    <t>Responsive UI</t>
-  </si>
-  <si>
-    <t>Validate Responsive UI scenario 1</t>
-  </si>
-  <si>
-    <t>TC_RUI_002</t>
-  </si>
-  <si>
-    <t>Validate Responsive UI scenario 2</t>
-  </si>
-  <si>
-    <t>TC_RUI_003</t>
-  </si>
-  <si>
-    <t>Validate Responsive UI scenario 3</t>
-  </si>
-  <si>
-    <t>TC_RUI_004</t>
-  </si>
-  <si>
-    <t>Validate Responsive UI scenario 4</t>
-  </si>
-  <si>
-    <t>TC_RUI_005</t>
-  </si>
-  <si>
-    <t>Validate Responsive UI scenario 5</t>
-  </si>
-  <si>
     <t>TC_F_001</t>
   </si>
   <si>
@@ -299,36 +266,6 @@
     <t>Validate Forms scenario 20</t>
   </si>
   <si>
-    <t>TC_F_021</t>
-  </si>
-  <si>
-    <t>Validate Forms scenario 21</t>
-  </si>
-  <si>
-    <t>TC_F_022</t>
-  </si>
-  <si>
-    <t>Validate Forms scenario 22</t>
-  </si>
-  <si>
-    <t>TC_F_023</t>
-  </si>
-  <si>
-    <t>Validate Forms scenario 23</t>
-  </si>
-  <si>
-    <t>TC_F_024</t>
-  </si>
-  <si>
-    <t>Validate Forms scenario 24</t>
-  </si>
-  <si>
-    <t>TC_F_025</t>
-  </si>
-  <si>
-    <t>Validate Forms scenario 25</t>
-  </si>
-  <si>
     <t>TC_N_001</t>
   </si>
   <si>
@@ -422,36 +359,6 @@
     <t>Validate Navigation scenario 15</t>
   </si>
   <si>
-    <t>TC_N_016</t>
-  </si>
-  <si>
-    <t>Validate Navigation scenario 16</t>
-  </si>
-  <si>
-    <t>TC_N_017</t>
-  </si>
-  <si>
-    <t>Validate Navigation scenario 17</t>
-  </si>
-  <si>
-    <t>TC_N_018</t>
-  </si>
-  <si>
-    <t>Validate Navigation scenario 18</t>
-  </si>
-  <si>
-    <t>TC_N_019</t>
-  </si>
-  <si>
-    <t>Validate Navigation scenario 19</t>
-  </si>
-  <si>
-    <t>TC_N_020</t>
-  </si>
-  <si>
-    <t>Validate Navigation scenario 20</t>
-  </si>
-  <si>
     <t>TC_A_001</t>
   </si>
   <si>
@@ -485,408 +392,486 @@
     <t>Validate Accessibility scenario 5</t>
   </si>
   <si>
+    <t>TC_VT_001</t>
+  </si>
+  <si>
+    <t>Vulnerability Tests</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 1</t>
+  </si>
+  <si>
+    <t>TC_VT_002</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 2</t>
+  </si>
+  <si>
+    <t>TC_VT_003</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 3</t>
+  </si>
+  <si>
+    <t>TC_VT_004</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 4</t>
+  </si>
+  <si>
+    <t>TC_VT_005</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 5</t>
+  </si>
+  <si>
+    <t>TC_VT_006</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 6</t>
+  </si>
+  <si>
+    <t>TC_VT_007</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 7</t>
+  </si>
+  <si>
+    <t>TC_VT_008</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 8</t>
+  </si>
+  <si>
+    <t>TC_VT_009</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 9</t>
+  </si>
+  <si>
+    <t>TC_VT_010</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 10</t>
+  </si>
+  <si>
+    <t>TC_VT_011</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 11</t>
+  </si>
+  <si>
+    <t>TC_VT_012</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 12</t>
+  </si>
+  <si>
+    <t>TC_VT_013</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 13</t>
+  </si>
+  <si>
+    <t>TC_VT_014</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 14</t>
+  </si>
+  <si>
+    <t>TC_VT_015</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 15</t>
+  </si>
+  <si>
+    <t>TC_VT_016</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 16</t>
+  </si>
+  <si>
+    <t>TC_VT_017</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 17</t>
+  </si>
+  <si>
+    <t>TC_VT_018</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 18</t>
+  </si>
+  <si>
+    <t>TC_VT_019</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 19</t>
+  </si>
+  <si>
+    <t>TC_VT_020</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 20</t>
+  </si>
+  <si>
+    <t>TC_VT_021</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 21</t>
+  </si>
+  <si>
+    <t>TC_VT_022</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 22</t>
+  </si>
+  <si>
+    <t>TC_VT_023</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 23</t>
+  </si>
+  <si>
+    <t>TC_VT_024</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 24</t>
+  </si>
+  <si>
+    <t>TC_VT_025</t>
+  </si>
+  <si>
+    <t>Validate Vulnerability Tests scenario 25</t>
+  </si>
+  <si>
+    <t>TC_D_001</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 1</t>
+  </si>
+  <si>
+    <t>TC_D_002</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 2</t>
+  </si>
+  <si>
+    <t>TC_D_003</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 3</t>
+  </si>
+  <si>
+    <t>TC_D_004</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 4</t>
+  </si>
+  <si>
+    <t>TC_D_005</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 5</t>
+  </si>
+  <si>
+    <t>TC_D_006</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 6</t>
+  </si>
+  <si>
+    <t>TC_D_007</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 7</t>
+  </si>
+  <si>
+    <t>TC_D_008</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 8</t>
+  </si>
+  <si>
+    <t>TC_D_009</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 9</t>
+  </si>
+  <si>
+    <t>TC_D_010</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 10</t>
+  </si>
+  <si>
+    <t>TC_D_011</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 11</t>
+  </si>
+  <si>
+    <t>TC_D_012</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 12</t>
+  </si>
+  <si>
+    <t>TC_D_013</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 13</t>
+  </si>
+  <si>
+    <t>TC_D_014</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 14</t>
+  </si>
+  <si>
+    <t>TC_D_015</t>
+  </si>
+  <si>
+    <t>Validate Dashboard scenario 15</t>
+  </si>
+  <si>
+    <t>TC_FU_001</t>
+  </si>
+  <si>
+    <t>File Upload</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 1</t>
+  </si>
+  <si>
+    <t>TC_FU_002</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 2</t>
+  </si>
+  <si>
+    <t>TC_FU_003</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 3</t>
+  </si>
+  <si>
+    <t>TC_FU_004</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 4</t>
+  </si>
+  <si>
+    <t>TC_FU_005</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 5</t>
+  </si>
+  <si>
+    <t>TC_FU_006</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 6</t>
+  </si>
+  <si>
+    <t>TC_FU_007</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 7</t>
+  </si>
+  <si>
+    <t>TC_FU_008</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 8</t>
+  </si>
+  <si>
+    <t>TC_FU_009</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 9</t>
+  </si>
+  <si>
+    <t>TC_FU_010</t>
+  </si>
+  <si>
+    <t>Validate File Upload scenario 10</t>
+  </si>
+  <si>
+    <t>TC_RS_001</t>
+  </si>
+  <si>
+    <t>Regression Suite</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 1</t>
+  </si>
+  <si>
+    <t>TC_RS_002</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 2</t>
+  </si>
+  <si>
+    <t>TC_RS_003</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 3</t>
+  </si>
+  <si>
+    <t>TC_RS_004</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 4</t>
+  </si>
+  <si>
+    <t>TC_RS_005</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 5</t>
+  </si>
+  <si>
+    <t>TC_RS_006</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 6</t>
+  </si>
+  <si>
+    <t>TC_RS_007</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 7</t>
+  </si>
+  <si>
+    <t>TC_RS_008</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 8</t>
+  </si>
+  <si>
+    <t>TC_RS_009</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 9</t>
+  </si>
+  <si>
+    <t>TC_RS_010</t>
+  </si>
+  <si>
+    <t>Validate Regression Suite scenario 10</t>
+  </si>
+  <si>
+    <t>TC_SM_001</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 1</t>
+  </si>
+  <si>
+    <t>TC_SM_002</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 2</t>
+  </si>
+  <si>
+    <t>TC_SM_003</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 3</t>
+  </si>
+  <si>
+    <t>TC_SM_004</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 4</t>
+  </si>
+  <si>
+    <t>TC_SM_005</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 5</t>
+  </si>
+  <si>
+    <t>TC_SM_006</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 6</t>
+  </si>
+  <si>
+    <t>TC_SM_007</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 7</t>
+  </si>
+  <si>
+    <t>TC_SM_008</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 8</t>
+  </si>
+  <si>
+    <t>TC_SM_009</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 9</t>
+  </si>
+  <si>
+    <t>TC_SM_010</t>
+  </si>
+  <si>
+    <t>Validate Session Management scenario 10</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Validate Authorization scenario 1</t>
+  </si>
+  <si>
+    <t>Validate Authorization scenario 2</t>
+  </si>
+  <si>
+    <t>Validate Authorization scenario 3</t>
+  </si>
+  <si>
+    <t>Validate Authorization scenario 4</t>
+  </si>
+  <si>
+    <t>Validate Authorization scenario 5</t>
+  </si>
+  <si>
     <t>TC_A_006</t>
   </si>
   <si>
-    <t>Validate Accessibility scenario 6</t>
+    <t>Validate Authorization scenario 6</t>
   </si>
   <si>
     <t>TC_A_007</t>
   </si>
   <si>
-    <t>Validate Accessibility scenario 7</t>
+    <t>Validate Authorization scenario 7</t>
   </si>
   <si>
     <t>TC_A_008</t>
   </si>
   <si>
-    <t>Validate Accessibility scenario 8</t>
+    <t>Validate Authorization scenario 8</t>
   </si>
   <si>
     <t>TC_A_009</t>
   </si>
   <si>
-    <t>Validate Accessibility scenario 9</t>
+    <t>Validate Authorization scenario 9</t>
   </si>
   <si>
     <t>TC_A_010</t>
   </si>
   <si>
-    <t>Validate Accessibility scenario 10</t>
-  </si>
-  <si>
-    <t>TC_D_001</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 1</t>
-  </si>
-  <si>
-    <t>TC_D_002</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 2</t>
-  </si>
-  <si>
-    <t>TC_D_003</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 3</t>
-  </si>
-  <si>
-    <t>TC_D_004</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 4</t>
-  </si>
-  <si>
-    <t>TC_D_005</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 5</t>
-  </si>
-  <si>
-    <t>TC_D_006</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 6</t>
-  </si>
-  <si>
-    <t>TC_D_007</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 7</t>
-  </si>
-  <si>
-    <t>TC_D_008</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 8</t>
-  </si>
-  <si>
-    <t>TC_D_009</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 9</t>
-  </si>
-  <si>
-    <t>TC_D_010</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 10</t>
-  </si>
-  <si>
-    <t>TC_D_011</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 11</t>
-  </si>
-  <si>
-    <t>TC_D_012</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 12</t>
-  </si>
-  <si>
-    <t>TC_D_013</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 13</t>
-  </si>
-  <si>
-    <t>TC_D_014</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 14</t>
-  </si>
-  <si>
-    <t>TC_D_015</t>
-  </si>
-  <si>
-    <t>Validate Dashboard scenario 15</t>
-  </si>
-  <si>
-    <t>TC_FU_001</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 1</t>
-  </si>
-  <si>
-    <t>TC_FU_002</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 2</t>
-  </si>
-  <si>
-    <t>TC_FU_003</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 3</t>
-  </si>
-  <si>
-    <t>TC_FU_004</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 4</t>
-  </si>
-  <si>
-    <t>TC_FU_005</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 5</t>
-  </si>
-  <si>
-    <t>TC_FU_006</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 6</t>
-  </si>
-  <si>
-    <t>TC_FU_007</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 7</t>
-  </si>
-  <si>
-    <t>TC_FU_008</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 8</t>
-  </si>
-  <si>
-    <t>TC_FU_009</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 9</t>
-  </si>
-  <si>
-    <t>TC_FU_010</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 10</t>
-  </si>
-  <si>
-    <t>TC_FU_011</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 11</t>
-  </si>
-  <si>
-    <t>TC_FU_012</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 12</t>
-  </si>
-  <si>
-    <t>TC_FU_013</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 13</t>
-  </si>
-  <si>
-    <t>TC_FU_014</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 14</t>
-  </si>
-  <si>
-    <t>TC_FU_015</t>
-  </si>
-  <si>
-    <t>Validate File Upload scenario 15</t>
-  </si>
-  <si>
-    <t>TC_RS_001</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 1</t>
-  </si>
-  <si>
-    <t>TC_RS_002</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 2</t>
-  </si>
-  <si>
-    <t>TC_RS_003</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 3</t>
-  </si>
-  <si>
-    <t>TC_RS_004</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 4</t>
-  </si>
-  <si>
-    <t>TC_RS_005</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 5</t>
-  </si>
-  <si>
-    <t>TC_RS_006</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 6</t>
-  </si>
-  <si>
-    <t>TC_RS_007</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 7</t>
-  </si>
-  <si>
-    <t>TC_RS_008</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 8</t>
-  </si>
-  <si>
-    <t>TC_RS_009</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 9</t>
-  </si>
-  <si>
-    <t>TC_RS_010</t>
-  </si>
-  <si>
-    <t>Validate Regression Suite scenario 10</t>
-  </si>
-  <si>
-    <t>TC_SM_001</t>
-  </si>
-  <si>
-    <t>Session Management</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 1</t>
-  </si>
-  <si>
-    <t>TC_SM_002</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 2</t>
-  </si>
-  <si>
-    <t>TC_SM_003</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 3</t>
-  </si>
-  <si>
-    <t>TC_SM_004</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 4</t>
-  </si>
-  <si>
-    <t>TC_SM_005</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 5</t>
-  </si>
-  <si>
-    <t>TC_SM_006</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 6</t>
-  </si>
-  <si>
-    <t>TC_SM_007</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 7</t>
-  </si>
-  <si>
-    <t>TC_SM_008</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 8</t>
-  </si>
-  <si>
-    <t>TC_SM_009</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 9</t>
-  </si>
-  <si>
-    <t>TC_SM_010</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 10</t>
-  </si>
-  <si>
-    <t>TC_SM_011</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 11</t>
-  </si>
-  <si>
-    <t>TC_SM_012</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 12</t>
-  </si>
-  <si>
-    <t>TC_SM_013</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 13</t>
-  </si>
-  <si>
-    <t>TC_SM_014</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 14</t>
-  </si>
-  <si>
-    <t>TC_SM_015</t>
-  </si>
-  <si>
-    <t>Validate Session Management scenario 15</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 1</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 2</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 3</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 4</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 5</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 6</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 7</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 8</t>
-  </si>
-  <si>
-    <t>Validate Authorization scenario 9</t>
-  </si>
-  <si>
     <t>Validate Authorization scenario 10</t>
   </si>
   <si>
@@ -983,21 +968,6 @@
     <t>Validate Filters scenario 10</t>
   </si>
   <si>
-    <t>Validate Filters scenario 11</t>
-  </si>
-  <si>
-    <t>Validate Filters scenario 12</t>
-  </si>
-  <si>
-    <t>Validate Filters scenario 13</t>
-  </si>
-  <si>
-    <t>Validate Filters scenario 14</t>
-  </si>
-  <si>
-    <t>Validate Filters scenario 15</t>
-  </si>
-  <si>
     <t>TC_PST_001</t>
   </si>
   <si>
@@ -1031,36 +1001,6 @@
     <t>Validate Performance Smoke Tests scenario 5</t>
   </si>
   <si>
-    <t>TC_PST_006</t>
-  </si>
-  <si>
-    <t>Validate Performance Smoke Tests scenario 6</t>
-  </si>
-  <si>
-    <t>TC_PST_007</t>
-  </si>
-  <si>
-    <t>Validate Performance Smoke Tests scenario 7</t>
-  </si>
-  <si>
-    <t>TC_PST_008</t>
-  </si>
-  <si>
-    <t>Validate Performance Smoke Tests scenario 8</t>
-  </si>
-  <si>
-    <t>TC_PST_009</t>
-  </si>
-  <si>
-    <t>Validate Performance Smoke Tests scenario 9</t>
-  </si>
-  <si>
-    <t>TC_PST_010</t>
-  </si>
-  <si>
-    <t>Validate Performance Smoke Tests scenario 10</t>
-  </si>
-  <si>
     <t>Authentication</t>
   </si>
   <si>
@@ -1154,36 +1094,6 @@
     <t>Validate Authentication scenario 25</t>
   </si>
   <si>
-    <t>TC_A_026</t>
-  </si>
-  <si>
-    <t>Validate Authentication scenario 26</t>
-  </si>
-  <si>
-    <t>TC_A_027</t>
-  </si>
-  <si>
-    <t>Validate Authentication scenario 27</t>
-  </si>
-  <si>
-    <t>TC_A_028</t>
-  </si>
-  <si>
-    <t>Validate Authentication scenario 28</t>
-  </si>
-  <si>
-    <t>TC_A_029</t>
-  </si>
-  <si>
-    <t>Validate Authentication scenario 29</t>
-  </si>
-  <si>
-    <t>TC_A_030</t>
-  </si>
-  <si>
-    <t>Validate Authentication scenario 30</t>
-  </si>
-  <si>
     <t>TC_R_001</t>
   </si>
   <si>
@@ -1340,36 +1250,6 @@
     <t>Validate Search scenario 10</t>
   </si>
   <si>
-    <t>TC_S_011</t>
-  </si>
-  <si>
-    <t>Validate Search scenario 11</t>
-  </si>
-  <si>
-    <t>TC_S_012</t>
-  </si>
-  <si>
-    <t>Validate Search scenario 12</t>
-  </si>
-  <si>
-    <t>TC_S_013</t>
-  </si>
-  <si>
-    <t>Validate Search scenario 13</t>
-  </si>
-  <si>
-    <t>TC_S_014</t>
-  </si>
-  <si>
-    <t>Validate Search scenario 14</t>
-  </si>
-  <si>
-    <t>TC_S_015</t>
-  </si>
-  <si>
-    <t>Validate Search scenario 15</t>
-  </si>
-  <si>
     <t>TC_IV_001</t>
   </si>
   <si>
@@ -1463,97 +1343,340 @@
     <t>Validate Input Validation scenario 15</t>
   </si>
   <si>
-    <t>TC_IV_016</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 16</t>
-  </si>
-  <si>
-    <t>TC_IV_017</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 17</t>
-  </si>
-  <si>
-    <t>TC_IV_018</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 18</t>
-  </si>
-  <si>
-    <t>TC_IV_019</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 19</t>
-  </si>
-  <si>
-    <t>TC_IV_020</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 20</t>
-  </si>
-  <si>
-    <t>TC_IV_021</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 21</t>
-  </si>
-  <si>
-    <t>TC_IV_022</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 22</t>
-  </si>
-  <si>
-    <t>TC_IV_023</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 23</t>
-  </si>
-  <si>
-    <t>TC_IV_024</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 24</t>
-  </si>
-  <si>
-    <t>TC_IV_025</t>
-  </si>
-  <si>
-    <t>Validate Input Validation scenario 25</t>
-  </si>
-  <si>
-    <t>TC_OH_001</t>
-  </si>
-  <si>
-    <t>Offline Handling</t>
-  </si>
-  <si>
-    <t>Validate Offline Handling scenario 1</t>
-  </si>
-  <si>
-    <t>TC_OH_002</t>
-  </si>
-  <si>
-    <t>Validate Offline Handling scenario 2</t>
-  </si>
-  <si>
-    <t>TC_OH_003</t>
-  </si>
-  <si>
-    <t>Validate Offline Handling scenario 3</t>
-  </si>
-  <si>
-    <t>TC_OH_004</t>
-  </si>
-  <si>
-    <t>Validate Offline Handling scenario 4</t>
-  </si>
-  <si>
-    <t>TC_OH_005</t>
-  </si>
-  <si>
-    <t>Validate Offline Handling scenario 5</t>
+    <t>TC_AMA_001</t>
+  </si>
+  <si>
+    <t>Appium Mobile Automation</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 1</t>
+  </si>
+  <si>
+    <t>TC_AMA_002</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 2</t>
+  </si>
+  <si>
+    <t>TC_AMA_003</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 3</t>
+  </si>
+  <si>
+    <t>TC_AMA_004</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 4</t>
+  </si>
+  <si>
+    <t>TC_AMA_005</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 5</t>
+  </si>
+  <si>
+    <t>TC_AMA_006</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 6</t>
+  </si>
+  <si>
+    <t>TC_AMA_007</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 7</t>
+  </si>
+  <si>
+    <t>TC_AMA_008</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 8</t>
+  </si>
+  <si>
+    <t>TC_AMA_009</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 9</t>
+  </si>
+  <si>
+    <t>TC_AMA_010</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 10</t>
+  </si>
+  <si>
+    <t>TC_AMA_011</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 11</t>
+  </si>
+  <si>
+    <t>TC_AMA_012</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 12</t>
+  </si>
+  <si>
+    <t>TC_AMA_013</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 13</t>
+  </si>
+  <si>
+    <t>TC_AMA_014</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 14</t>
+  </si>
+  <si>
+    <t>TC_AMA_015</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 15</t>
+  </si>
+  <si>
+    <t>TC_AMA_016</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 16</t>
+  </si>
+  <si>
+    <t>TC_AMA_017</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 17</t>
+  </si>
+  <si>
+    <t>TC_AMA_018</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 18</t>
+  </si>
+  <si>
+    <t>TC_AMA_019</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 19</t>
+  </si>
+  <si>
+    <t>TC_AMA_020</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 20</t>
+  </si>
+  <si>
+    <t>TC_AMA_021</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 21</t>
+  </si>
+  <si>
+    <t>TC_AMA_022</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 22</t>
+  </si>
+  <si>
+    <t>TC_AMA_023</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 23</t>
+  </si>
+  <si>
+    <t>TC_AMA_024</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 24</t>
+  </si>
+  <si>
+    <t>TC_AMA_025</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 25</t>
+  </si>
+  <si>
+    <t>TC_AMA_026</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 26</t>
+  </si>
+  <si>
+    <t>TC_AMA_027</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 27</t>
+  </si>
+  <si>
+    <t>TC_AMA_028</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 28</t>
+  </si>
+  <si>
+    <t>TC_AMA_029</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 29</t>
+  </si>
+  <si>
+    <t>TC_AMA_030</t>
+  </si>
+  <si>
+    <t>Validate Appium Mobile Automation scenario 30</t>
+  </si>
+  <si>
+    <t>TC_ST_001</t>
+  </si>
+  <si>
+    <t>Security Tests</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 1</t>
+  </si>
+  <si>
+    <t>TC_ST_002</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 2</t>
+  </si>
+  <si>
+    <t>TC_ST_003</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 3</t>
+  </si>
+  <si>
+    <t>TC_ST_004</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 4</t>
+  </si>
+  <si>
+    <t>TC_ST_005</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 5</t>
+  </si>
+  <si>
+    <t>TC_ST_006</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 6</t>
+  </si>
+  <si>
+    <t>TC_ST_007</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 7</t>
+  </si>
+  <si>
+    <t>TC_ST_008</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 8</t>
+  </si>
+  <si>
+    <t>TC_ST_009</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 9</t>
+  </si>
+  <si>
+    <t>TC_ST_010</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 10</t>
+  </si>
+  <si>
+    <t>TC_ST_011</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 11</t>
+  </si>
+  <si>
+    <t>TC_ST_012</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 12</t>
+  </si>
+  <si>
+    <t>TC_ST_013</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 13</t>
+  </si>
+  <si>
+    <t>TC_ST_014</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 14</t>
+  </si>
+  <si>
+    <t>TC_ST_015</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 15</t>
+  </si>
+  <si>
+    <t>TC_ST_016</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 16</t>
+  </si>
+  <si>
+    <t>TC_ST_017</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 17</t>
+  </si>
+  <si>
+    <t>TC_ST_018</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 18</t>
+  </si>
+  <si>
+    <t>TC_ST_019</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 19</t>
+  </si>
+  <si>
+    <t>TC_ST_020</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 20</t>
+  </si>
+  <si>
+    <t>TC_ST_021</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 21</t>
+  </si>
+  <si>
+    <t>TC_ST_022</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 22</t>
+  </si>
+  <si>
+    <t>TC_ST_023</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 23</t>
+  </si>
+  <si>
+    <t>TC_ST_024</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 24</t>
+  </si>
+  <si>
+    <t>TC_ST_025</t>
+  </si>
+  <si>
+    <t>Validate Security Tests scenario 25</t>
   </si>
   <si>
     <t>TC_EH_001</t>
@@ -1619,84 +1742,6 @@
     <t>Validate Error Handling scenario 10</t>
   </si>
   <si>
-    <t>TC_EH_011</t>
-  </si>
-  <si>
-    <t>Validate Error Handling scenario 11</t>
-  </si>
-  <si>
-    <t>TC_EH_012</t>
-  </si>
-  <si>
-    <t>Validate Error Handling scenario 12</t>
-  </si>
-  <si>
-    <t>TC_EH_013</t>
-  </si>
-  <si>
-    <t>Validate Error Handling scenario 13</t>
-  </si>
-  <si>
-    <t>TC_EH_014</t>
-  </si>
-  <si>
-    <t>Validate Error Handling scenario 14</t>
-  </si>
-  <si>
-    <t>TC_EH_015</t>
-  </si>
-  <si>
-    <t>Validate Error Handling scenario 15</t>
-  </si>
-  <si>
-    <t>Notifications</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 1</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 2</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 3</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 4</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 5</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 6</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 7</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 8</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 9</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 10</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 11</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 12</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 13</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 14</t>
-  </si>
-  <si>
-    <t>Validate Notifications scenario 15</t>
-  </si>
-  <si>
     <t>TC_CRUD_001</t>
   </si>
   <si>
@@ -1818,36 +1863,6 @@
   </si>
   <si>
     <t>Validate CRUD Operations scenario 20</t>
-  </si>
-  <si>
-    <t>TC_CRUD_021</t>
-  </si>
-  <si>
-    <t>Validate CRUD Operations scenario 21</t>
-  </si>
-  <si>
-    <t>TC_CRUD_022</t>
-  </si>
-  <si>
-    <t>Validate CRUD Operations scenario 22</t>
-  </si>
-  <si>
-    <t>TC_CRUD_023</t>
-  </si>
-  <si>
-    <t>Validate CRUD Operations scenario 23</t>
-  </si>
-  <si>
-    <t>TC_CRUD_024</t>
-  </si>
-  <si>
-    <t>Validate CRUD Operations scenario 24</t>
-  </si>
-  <si>
-    <t>TC_CRUD_025</t>
-  </si>
-  <si>
-    <t>Validate CRUD Operations scenario 25</t>
   </si>
 </sst>
 </file>
@@ -1909,12 +1924,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G321"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.51171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="38.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.34375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="40.02734375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="8.24609375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.5546875" customWidth="true" bestFit="true"/>
@@ -1961,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>12</v>
@@ -1984,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>26.0</v>
+        <v>18.0</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>12</v>
@@ -2007,7 +2022,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>12</v>
@@ -2030,7 +2045,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>12</v>
@@ -2076,7 +2091,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>12</v>
@@ -2099,7 +2114,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>12</v>
@@ -2122,7 +2137,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>12</v>
@@ -2145,7 +2160,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>12</v>
@@ -2168,7 +2183,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>12</v>
@@ -2191,7 +2206,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>12</v>
@@ -2237,7 +2252,7 @@
         <v>11</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>12</v>
@@ -2260,7 +2275,7 @@
         <v>11</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>12</v>
@@ -2306,7 +2321,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>12</v>
@@ -2329,7 +2344,7 @@
         <v>11</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>12</v>
@@ -2352,7 +2367,7 @@
         <v>11</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>12</v>
@@ -2375,7 +2390,7 @@
         <v>11</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>12</v>
@@ -2398,7 +2413,7 @@
         <v>11</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>16.0</v>
+        <v>26.0</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>12</v>
@@ -2409,19 +2424,19 @@
         <v>54</v>
       </c>
       <c r="B22" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="C22" t="s" s="0">
-        <v>56</v>
-      </c>
       <c r="D22" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>15.0</v>
+        <v>27.0</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>12</v>
@@ -2429,22 +2444,22 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>58</v>
-      </c>
       <c r="D23" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>12</v>
@@ -2452,22 +2467,22 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="B24" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>60</v>
-      </c>
       <c r="D24" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>12</v>
@@ -2475,22 +2490,22 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="B25" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>62</v>
-      </c>
       <c r="D25" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>12</v>
@@ -2498,22 +2513,22 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="B26" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>64</v>
-      </c>
       <c r="D26" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>12</v>
@@ -2521,22 +2536,22 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="B27" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>66</v>
-      </c>
       <c r="D27" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>12</v>
@@ -2544,22 +2559,22 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="B28" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>68</v>
-      </c>
       <c r="D28" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>12</v>
@@ -2567,22 +2582,22 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="B29" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>70</v>
-      </c>
       <c r="D29" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>12</v>
@@ -2590,22 +2605,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="B30" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>72</v>
-      </c>
       <c r="D30" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>12</v>
@@ -2613,22 +2628,22 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="B31" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>74</v>
-      </c>
       <c r="D31" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>12</v>
@@ -2636,22 +2651,22 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="B32" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s" s="0">
-        <v>76</v>
-      </c>
       <c r="D32" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>12</v>
@@ -2659,16 +2674,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="B33" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C33" t="s" s="0">
-        <v>78</v>
-      </c>
       <c r="D33" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>11</v>
@@ -2682,16 +2697,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B34" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C34" t="s" s="0">
-        <v>80</v>
-      </c>
       <c r="D34" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>11</v>
@@ -2705,22 +2720,22 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="B35" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>82</v>
-      </c>
       <c r="D35" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>12</v>
@@ -2728,22 +2743,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="B36" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C36" t="s" s="0">
-        <v>84</v>
-      </c>
       <c r="D36" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>12</v>
@@ -2751,10 +2766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B37" t="s" s="0">
         <v>85</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>55</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>86</v>
@@ -2766,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>12</v>
@@ -2777,7 +2792,7 @@
         <v>87</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>88</v>
@@ -2789,7 +2804,7 @@
         <v>11</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>12</v>
@@ -2800,7 +2815,7 @@
         <v>89</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>90</v>
@@ -2812,7 +2827,7 @@
         <v>11</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>12</v>
@@ -2823,7 +2838,7 @@
         <v>91</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>92</v>
@@ -2835,7 +2850,7 @@
         <v>11</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>12</v>
@@ -2846,7 +2861,7 @@
         <v>93</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>94</v>
@@ -2858,7 +2873,7 @@
         <v>11</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>12</v>
@@ -2869,7 +2884,7 @@
         <v>95</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>96</v>
@@ -2881,7 +2896,7 @@
         <v>11</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="G42" t="s" s="0">
         <v>12</v>
@@ -2892,7 +2907,7 @@
         <v>97</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>98</v>
@@ -2904,7 +2919,7 @@
         <v>11</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>22.0</v>
+        <v>13.0</v>
       </c>
       <c r="G43" t="s" s="0">
         <v>12</v>
@@ -2915,7 +2930,7 @@
         <v>99</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>100</v>
@@ -2927,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G44" t="s" s="0">
         <v>12</v>
@@ -2938,7 +2953,7 @@
         <v>101</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>102</v>
@@ -2950,7 +2965,7 @@
         <v>11</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G45" t="s" s="0">
         <v>12</v>
@@ -2961,7 +2976,7 @@
         <v>103</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>104</v>
@@ -2973,7 +2988,7 @@
         <v>11</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G46" t="s" s="0">
         <v>12</v>
@@ -2984,19 +2999,19 @@
         <v>105</v>
       </c>
       <c r="B47" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="C47" t="s" s="0">
-        <v>107</v>
-      </c>
       <c r="D47" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G47" t="s" s="0">
         <v>12</v>
@@ -3004,16 +3019,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C48" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B48" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>109</v>
-      </c>
       <c r="D48" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>11</v>
@@ -3027,22 +3042,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C49" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="B49" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="C49" t="s" s="0">
-        <v>111</v>
-      </c>
       <c r="D49" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>12</v>
@@ -3050,22 +3065,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C50" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="B50" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="C50" t="s" s="0">
-        <v>113</v>
-      </c>
       <c r="D50" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>12</v>
@@ -3073,22 +3088,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C51" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B51" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="C51" t="s" s="0">
-        <v>115</v>
-      </c>
       <c r="D51" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>12</v>
@@ -3096,22 +3111,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s" s="0">
         <v>116</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>106</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>117</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F52" t="n" s="0">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>12</v>
@@ -3122,19 +3137,19 @@
         <v>118</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>119</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>15.0</v>
+        <v>31.0</v>
       </c>
       <c r="G53" t="s" s="0">
         <v>12</v>
@@ -3145,19 +3160,19 @@
         <v>120</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>121</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G54" t="s" s="0">
         <v>12</v>
@@ -3168,19 +3183,19 @@
         <v>122</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>123</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G55" t="s" s="0">
         <v>12</v>
@@ -3191,19 +3206,19 @@
         <v>124</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>125</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="G56" t="s" s="0">
         <v>12</v>
@@ -3214,19 +3229,19 @@
         <v>126</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="G57" t="s" s="0">
         <v>12</v>
@@ -3234,22 +3249,22 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G58" t="s" s="0">
         <v>12</v>
@@ -3257,22 +3272,22 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="G59" t="s" s="0">
         <v>12</v>
@@ -3280,22 +3295,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G60" t="s" s="0">
         <v>12</v>
@@ -3303,22 +3318,22 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G61" t="s" s="0">
         <v>12</v>
@@ -3326,16 +3341,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>11</v>
@@ -3349,22 +3364,22 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G63" t="s" s="0">
         <v>12</v>
@@ -3372,22 +3387,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="G64" t="s" s="0">
         <v>12</v>
@@ -3395,16 +3410,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>11</v>
@@ -3418,22 +3433,22 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G66" t="s" s="0">
         <v>12</v>
@@ -3441,22 +3456,22 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s" s="0">
         <v>148</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G67" t="s" s="0">
         <v>12</v>
@@ -3467,19 +3482,19 @@
         <v>149</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s" s="0">
         <v>150</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="G68" t="s" s="0">
         <v>12</v>
@@ -3490,13 +3505,13 @@
         <v>151</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s" s="0">
         <v>152</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>11</v>
@@ -3513,19 +3528,19 @@
         <v>153</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s" s="0">
         <v>154</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>68.0</v>
+        <v>24.0</v>
       </c>
       <c r="G70" t="s" s="0">
         <v>12</v>
@@ -3536,19 +3551,19 @@
         <v>155</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C71" t="s" s="0">
         <v>156</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>66.0</v>
+        <v>17.0</v>
       </c>
       <c r="G71" t="s" s="0">
         <v>12</v>
@@ -3559,19 +3574,19 @@
         <v>157</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C72" t="s" s="0">
         <v>158</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="G72" t="s" s="0">
         <v>12</v>
@@ -3582,19 +3597,19 @@
         <v>159</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s" s="0">
         <v>160</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F73" t="n" s="0">
-        <v>119.0</v>
+        <v>16.0</v>
       </c>
       <c r="G73" t="s" s="0">
         <v>12</v>
@@ -3605,19 +3620,19 @@
         <v>161</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s" s="0">
         <v>162</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>130.0</v>
+        <v>14.0</v>
       </c>
       <c r="G74" t="s" s="0">
         <v>12</v>
@@ -3628,19 +3643,19 @@
         <v>163</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s" s="0">
         <v>164</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>36.0</v>
+        <v>24.0</v>
       </c>
       <c r="G75" t="s" s="0">
         <v>12</v>
@@ -3651,19 +3666,19 @@
         <v>165</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s" s="0">
         <v>166</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>47.0</v>
+        <v>17.0</v>
       </c>
       <c r="G76" t="s" s="0">
         <v>12</v>
@@ -3674,19 +3689,19 @@
         <v>167</v>
       </c>
       <c r="B77" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C77" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="C77" t="s" s="0">
-        <v>169</v>
-      </c>
       <c r="D77" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G77" t="s" s="0">
         <v>12</v>
@@ -3694,22 +3709,22 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C78" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="B78" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="C78" t="s" s="0">
-        <v>171</v>
-      </c>
       <c r="D78" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="G78" t="s" s="0">
         <v>12</v>
@@ -3717,22 +3732,22 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B79" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="C79" t="s" s="0">
-        <v>173</v>
-      </c>
       <c r="D79" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="G79" t="s" s="0">
         <v>12</v>
@@ -3740,22 +3755,22 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C80" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="B80" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="C80" t="s" s="0">
-        <v>175</v>
-      </c>
       <c r="D80" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="G80" t="s" s="0">
         <v>12</v>
@@ -3763,22 +3778,22 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C81" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="B81" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="C81" t="s" s="0">
-        <v>177</v>
-      </c>
       <c r="D81" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>26.0</v>
+        <v>17.0</v>
       </c>
       <c r="G81" t="s" s="0">
         <v>12</v>
@@ -3786,22 +3801,22 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B82" t="s" s="0">
         <v>178</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="C82" t="s" s="0">
         <v>179</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>26.0</v>
+        <v>16.0</v>
       </c>
       <c r="G82" t="s" s="0">
         <v>12</v>
@@ -3812,13 +3827,13 @@
         <v>180</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s" s="0">
         <v>181</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>11</v>
@@ -3835,19 +3850,19 @@
         <v>182</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s" s="0">
         <v>183</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G84" t="s" s="0">
         <v>12</v>
@@ -3858,19 +3873,19 @@
         <v>184</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s" s="0">
         <v>185</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="G85" t="s" s="0">
         <v>12</v>
@@ -3881,19 +3896,19 @@
         <v>186</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C86" t="s" s="0">
         <v>187</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G86" t="s" s="0">
         <v>12</v>
@@ -3904,19 +3919,19 @@
         <v>188</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C87" t="s" s="0">
         <v>189</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="G87" t="s" s="0">
         <v>12</v>
@@ -3927,19 +3942,19 @@
         <v>190</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s" s="0">
         <v>191</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F88" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G88" t="s" s="0">
         <v>12</v>
@@ -3950,19 +3965,19 @@
         <v>192</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C89" t="s" s="0">
         <v>193</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F89" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="G89" t="s" s="0">
         <v>12</v>
@@ -3973,19 +3988,19 @@
         <v>194</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s" s="0">
         <v>195</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G90" t="s" s="0">
         <v>12</v>
@@ -3996,19 +4011,19 @@
         <v>196</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s" s="0">
         <v>197</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F91" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="G91" t="s" s="0">
         <v>12</v>
@@ -4019,19 +4034,19 @@
         <v>198</v>
       </c>
       <c r="B92" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C92" t="s" s="0">
         <v>199</v>
       </c>
-      <c r="C92" t="s" s="0">
-        <v>200</v>
-      </c>
       <c r="D92" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F92" t="n" s="0">
-        <v>30.0</v>
+        <v>16.0</v>
       </c>
       <c r="G92" t="s" s="0">
         <v>12</v>
@@ -4039,22 +4054,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C93" t="s" s="0">
         <v>201</v>
       </c>
-      <c r="B93" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="C93" t="s" s="0">
-        <v>202</v>
-      </c>
       <c r="D93" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="G93" t="s" s="0">
         <v>12</v>
@@ -4062,22 +4077,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C94" t="s" s="0">
         <v>203</v>
       </c>
-      <c r="B94" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="C94" t="s" s="0">
-        <v>204</v>
-      </c>
       <c r="D94" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F94" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G94" t="s" s="0">
         <v>12</v>
@@ -4085,22 +4100,22 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C95" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="B95" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="C95" t="s" s="0">
-        <v>206</v>
-      </c>
       <c r="D95" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F95" t="n" s="0">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="G95" t="s" s="0">
         <v>12</v>
@@ -4108,22 +4123,22 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C96" t="s" s="0">
         <v>207</v>
       </c>
-      <c r="B96" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="C96" t="s" s="0">
-        <v>208</v>
-      </c>
       <c r="D96" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F96" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G96" t="s" s="0">
         <v>12</v>
@@ -4131,22 +4146,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B97" t="s" s="0">
         <v>209</v>
-      </c>
-      <c r="B97" t="s" s="0">
-        <v>199</v>
       </c>
       <c r="C97" t="s" s="0">
         <v>210</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F97" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="G97" t="s" s="0">
         <v>12</v>
@@ -4157,19 +4172,19 @@
         <v>211</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C98" t="s" s="0">
         <v>212</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F98" t="n" s="0">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="G98" t="s" s="0">
         <v>12</v>
@@ -4180,19 +4195,19 @@
         <v>213</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s" s="0">
         <v>214</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="G99" t="s" s="0">
         <v>12</v>
@@ -4203,19 +4218,19 @@
         <v>215</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C100" t="s" s="0">
         <v>216</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G100" t="s" s="0">
         <v>12</v>
@@ -4226,13 +4241,13 @@
         <v>217</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C101" t="s" s="0">
         <v>218</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>11</v>
@@ -4249,19 +4264,19 @@
         <v>219</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C102" t="s" s="0">
         <v>220</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F102" t="n" s="0">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="G102" t="s" s="0">
         <v>12</v>
@@ -4272,19 +4287,19 @@
         <v>221</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C103" t="s" s="0">
         <v>222</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F103" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="G103" t="s" s="0">
         <v>12</v>
@@ -4295,19 +4310,19 @@
         <v>223</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C104" t="s" s="0">
         <v>224</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F104" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G104" t="s" s="0">
         <v>12</v>
@@ -4318,13 +4333,13 @@
         <v>225</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C105" t="s" s="0">
         <v>226</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>11</v>
@@ -4341,19 +4356,19 @@
         <v>227</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C106" t="s" s="0">
         <v>228</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F106" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G106" t="s" s="0">
         <v>12</v>
@@ -4376,7 +4391,7 @@
         <v>11</v>
       </c>
       <c r="F107" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G107" t="s" s="0">
         <v>12</v>
@@ -4399,7 +4414,7 @@
         <v>11</v>
       </c>
       <c r="F108" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G108" t="s" s="0">
         <v>12</v>
@@ -4422,7 +4437,7 @@
         <v>11</v>
       </c>
       <c r="F109" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G109" t="s" s="0">
         <v>12</v>
@@ -4445,7 +4460,7 @@
         <v>11</v>
       </c>
       <c r="F110" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G110" t="s" s="0">
         <v>12</v>
@@ -4468,7 +4483,7 @@
         <v>11</v>
       </c>
       <c r="F111" t="n" s="0">
-        <v>14.0</v>
+        <v>23.0</v>
       </c>
       <c r="G111" t="s" s="0">
         <v>12</v>
@@ -4491,7 +4506,7 @@
         <v>11</v>
       </c>
       <c r="F112" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G112" t="s" s="0">
         <v>12</v>
@@ -4514,7 +4529,7 @@
         <v>11</v>
       </c>
       <c r="F113" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>12</v>
@@ -4537,7 +4552,7 @@
         <v>11</v>
       </c>
       <c r="F114" t="n" s="0">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>12</v>
@@ -4560,7 +4575,7 @@
         <v>11</v>
       </c>
       <c r="F115" t="n" s="0">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>12</v>
@@ -4583,7 +4598,7 @@
         <v>11</v>
       </c>
       <c r="F116" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="G116" t="s" s="0">
         <v>12</v>
@@ -4606,7 +4621,7 @@
         <v>11</v>
       </c>
       <c r="F117" t="n" s="0">
-        <v>40.0</v>
+        <v>23.0</v>
       </c>
       <c r="G117" t="s" s="0">
         <v>12</v>
@@ -4629,7 +4644,7 @@
         <v>11</v>
       </c>
       <c r="F118" t="n" s="0">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
       <c r="G118" t="s" s="0">
         <v>12</v>
@@ -4652,7 +4667,7 @@
         <v>11</v>
       </c>
       <c r="F119" t="n" s="0">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="G119" t="s" s="0">
         <v>12</v>
@@ -4675,7 +4690,7 @@
         <v>11</v>
       </c>
       <c r="F120" t="n" s="0">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="G120" t="s" s="0">
         <v>12</v>
@@ -4698,7 +4713,7 @@
         <v>11</v>
       </c>
       <c r="F121" t="n" s="0">
-        <v>26.0</v>
+        <v>17.0</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>12</v>
@@ -4744,7 +4759,7 @@
         <v>11</v>
       </c>
       <c r="F123" t="n" s="0">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>12</v>
@@ -4767,7 +4782,7 @@
         <v>11</v>
       </c>
       <c r="F124" t="n" s="0">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="G124" t="s" s="0">
         <v>12</v>
@@ -4790,7 +4805,7 @@
         <v>11</v>
       </c>
       <c r="F125" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G125" t="s" s="0">
         <v>12</v>
@@ -4821,22 +4836,22 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B127" t="s" s="0">
         <v>271</v>
-      </c>
-      <c r="B127" t="s" s="0">
-        <v>251</v>
       </c>
       <c r="C127" t="s" s="0">
         <v>272</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F127" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G127" t="s" s="0">
         <v>12</v>
@@ -4844,16 +4859,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="C128" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="B128" t="s" s="0">
-        <v>251</v>
-      </c>
-      <c r="C128" t="s" s="0">
-        <v>274</v>
-      </c>
       <c r="D128" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E128" t="s" s="0">
         <v>11</v>
@@ -4867,22 +4882,22 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F129" t="n" s="0">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="G129" t="s" s="0">
         <v>12</v>
@@ -4890,22 +4905,22 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F130" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G130" t="s" s="0">
         <v>12</v>
@@ -4913,22 +4928,22 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>279</v>
+        <v>124</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E131" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F131" t="n" s="0">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
       <c r="G131" t="s" s="0">
         <v>12</v>
@@ -4936,22 +4951,22 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>146</v>
+        <v>277</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F132" t="n" s="0">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G132" t="s" s="0">
         <v>12</v>
@@ -4959,16 +4974,16 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>149</v>
+        <v>279</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E133" t="s" s="0">
         <v>11</v>
@@ -4982,22 +4997,22 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>151</v>
+        <v>281</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E134" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F134" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G134" t="s" s="0">
         <v>12</v>
@@ -5005,22 +5020,22 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>153</v>
+        <v>283</v>
       </c>
       <c r="B135" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E135" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F135" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G135" t="s" s="0">
         <v>12</v>
@@ -5028,22 +5043,22 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C136" t="s" s="0">
         <v>286</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F136" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G136" t="s" s="0">
         <v>12</v>
@@ -5051,22 +5066,22 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>157</v>
+        <v>287</v>
       </c>
       <c r="B137" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D137" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E137" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F137" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G137" t="s" s="0">
         <v>12</v>
@@ -5074,22 +5089,22 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>159</v>
+        <v>289</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E138" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F138" t="n" s="0">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="G138" t="s" s="0">
         <v>12</v>
@@ -5097,22 +5112,22 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>161</v>
+        <v>291</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F139" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G139" t="s" s="0">
         <v>12</v>
@@ -5120,16 +5135,16 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E140" t="s" s="0">
         <v>11</v>
@@ -5143,22 +5158,22 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="B141" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E141" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F141" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G141" t="s" s="0">
         <v>12</v>
@@ -5166,16 +5181,16 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B142" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E142" t="s" s="0">
         <v>11</v>
@@ -5189,16 +5204,16 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B143" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C143" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D143" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E143" t="s" s="0">
         <v>11</v>
@@ -5212,22 +5227,22 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F144" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G144" t="s" s="0">
         <v>12</v>
@@ -5235,22 +5250,22 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E145" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F145" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G145" t="s" s="0">
         <v>12</v>
@@ -5258,22 +5273,22 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B146" t="s" s="0">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D146" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F146" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G146" t="s" s="0">
         <v>12</v>
@@ -5281,13 +5296,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>302</v>
+        <v>43</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D147" t="s" s="0">
         <v>10</v>
@@ -5296,7 +5311,7 @@
         <v>11</v>
       </c>
       <c r="F147" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G147" t="s" s="0">
         <v>12</v>
@@ -5304,13 +5319,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>304</v>
+        <v>46</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D148" t="s" s="0">
         <v>15</v>
@@ -5319,7 +5334,7 @@
         <v>11</v>
       </c>
       <c r="F148" t="n" s="0">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
       <c r="G148" t="s" s="0">
         <v>12</v>
@@ -5327,13 +5342,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D149" t="s" s="0">
         <v>18</v>
@@ -5342,7 +5357,7 @@
         <v>11</v>
       </c>
       <c r="F149" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G149" t="s" s="0">
         <v>12</v>
@@ -5350,13 +5365,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>308</v>
+        <v>50</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D150" t="s" s="0">
         <v>10</v>
@@ -5365,7 +5380,7 @@
         <v>11</v>
       </c>
       <c r="F150" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G150" t="s" s="0">
         <v>12</v>
@@ -5373,13 +5388,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>310</v>
+        <v>52</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D151" t="s" s="0">
         <v>15</v>
@@ -5388,7 +5403,7 @@
         <v>11</v>
       </c>
       <c r="F151" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G151" t="s" s="0">
         <v>12</v>
@@ -5399,19 +5414,19 @@
         <v>54</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C152" t="s" s="0">
         <v>313</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E152" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F152" t="n" s="0">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="G152" t="s" s="0">
         <v>12</v>
@@ -5419,22 +5434,22 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C153" t="s" s="0">
         <v>314</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E153" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F153" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G153" t="s" s="0">
         <v>12</v>
@@ -5442,22 +5457,22 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C154" t="s" s="0">
         <v>315</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E154" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F154" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G154" t="s" s="0">
         <v>12</v>
@@ -5465,22 +5480,22 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C155" t="s" s="0">
         <v>316</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E155" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F155" t="n" s="0">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="G155" t="s" s="0">
         <v>12</v>
@@ -5488,16 +5503,16 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C156" t="s" s="0">
         <v>317</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E156" t="s" s="0">
         <v>11</v>
@@ -5511,22 +5526,22 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>65</v>
+        <v>318</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F157" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G157" t="s" s="0">
         <v>12</v>
@@ -5534,22 +5549,22 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E158" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F158" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G158" t="s" s="0">
         <v>12</v>
@@ -5557,22 +5572,22 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E159" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F159" t="n" s="0">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="G159" t="s" s="0">
         <v>12</v>
@@ -5580,22 +5595,22 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F160" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G160" t="s" s="0">
         <v>12</v>
@@ -5603,22 +5618,22 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E161" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F161" t="n" s="0">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="G161" t="s" s="0">
         <v>12</v>
@@ -5626,22 +5641,22 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E162" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F162" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G162" t="s" s="0">
         <v>12</v>
@@ -5649,22 +5664,22 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="B163" t="s" s="0">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D163" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F163" t="n" s="0">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="G163" t="s" s="0">
         <v>12</v>
@@ -5672,16 +5687,16 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E164" t="s" s="0">
         <v>11</v>
@@ -5695,22 +5710,22 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D165" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F165" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G165" t="s" s="0">
         <v>12</v>
@@ -5718,22 +5733,22 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F166" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G166" t="s" s="0">
         <v>12</v>
@@ -5741,22 +5756,22 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="B167" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D167" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E167" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F167" t="n" s="0">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="G167" t="s" s="0">
         <v>12</v>
@@ -5764,22 +5779,22 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="B168" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E168" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F168" t="n" s="0">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="G168" t="s" s="0">
         <v>12</v>
@@ -5787,22 +5802,22 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="B169" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F169" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G169" t="s" s="0">
         <v>12</v>
@@ -5810,22 +5825,22 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="B170" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E170" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F170" t="n" s="0">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G170" t="s" s="0">
         <v>12</v>
@@ -5833,16 +5848,16 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="B171" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E171" t="s" s="0">
         <v>11</v>
@@ -5856,7 +5871,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>339</v>
+        <v>287</v>
       </c>
       <c r="B172" t="s" s="0">
         <v>329</v>
@@ -5865,13 +5880,13 @@
         <v>340</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F172" t="n" s="0">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="G172" t="s" s="0">
         <v>12</v>
@@ -5879,22 +5894,22 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>341</v>
+        <v>289</v>
       </c>
       <c r="B173" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E173" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F173" t="n" s="0">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G173" t="s" s="0">
         <v>12</v>
@@ -5902,22 +5917,22 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="B174" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D174" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E174" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F174" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G174" t="s" s="0">
         <v>12</v>
@@ -5925,22 +5940,22 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="B175" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D175" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E175" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F175" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G175" t="s" s="0">
         <v>12</v>
@@ -5948,22 +5963,22 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="B176" t="s" s="0">
         <v>329</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D176" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E176" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F176" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G176" t="s" s="0">
         <v>12</v>
@@ -5971,13 +5986,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D177" t="s" s="0">
         <v>10</v>
@@ -5994,13 +6009,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>149</v>
+        <v>299</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D178" t="s" s="0">
         <v>15</v>
@@ -6009,7 +6024,7 @@
         <v>11</v>
       </c>
       <c r="F178" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G178" t="s" s="0">
         <v>12</v>
@@ -6017,13 +6032,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
-        <v>151</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C179" t="s" s="0">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D179" t="s" s="0">
         <v>18</v>
@@ -6032,7 +6047,7 @@
         <v>11</v>
       </c>
       <c r="F179" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G179" t="s" s="0">
         <v>12</v>
@@ -6040,13 +6055,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D180" t="s" s="0">
         <v>10</v>
@@ -6055,7 +6070,7 @@
         <v>11</v>
       </c>
       <c r="F180" t="n" s="0">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G180" t="s" s="0">
         <v>12</v>
@@ -6063,14 +6078,14 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>155</v>
+        <v>305</v>
       </c>
       <c r="B181" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="C181" t="s" s="0">
         <v>349</v>
       </c>
-      <c r="C181" t="s" s="0">
-        <v>354</v>
-      </c>
       <c r="D181" t="s" s="0">
         <v>15</v>
       </c>
@@ -6078,7 +6093,7 @@
         <v>11</v>
       </c>
       <c r="F181" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G181" t="s" s="0">
         <v>12</v>
@@ -6086,13 +6101,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>157</v>
+        <v>350</v>
       </c>
       <c r="B182" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D182" t="s" s="0">
         <v>18</v>
@@ -6101,7 +6116,7 @@
         <v>11</v>
       </c>
       <c r="F182" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="G182" t="s" s="0">
         <v>12</v>
@@ -6109,13 +6124,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>159</v>
+        <v>352</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D183" t="s" s="0">
         <v>10</v>
@@ -6124,7 +6139,7 @@
         <v>11</v>
       </c>
       <c r="F183" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="G183" t="s" s="0">
         <v>12</v>
@@ -6132,13 +6147,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>161</v>
+        <v>354</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D184" t="s" s="0">
         <v>15</v>
@@ -6155,13 +6170,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="B185" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C185" t="s" s="0">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D185" t="s" s="0">
         <v>18</v>
@@ -6178,10 +6193,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>165</v>
+        <v>358</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C186" t="s" s="0">
         <v>359</v>
@@ -6201,22 +6216,22 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>292</v>
+        <v>360</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D187" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E187" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F187" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G187" t="s" s="0">
         <v>12</v>
@@ -6224,22 +6239,22 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D188" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F188" t="n" s="0">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="G188" t="s" s="0">
         <v>12</v>
@@ -6247,22 +6262,22 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>296</v>
+        <v>365</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D189" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E189" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F189" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G189" t="s" s="0">
         <v>12</v>
@@ -6270,16 +6285,16 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>298</v>
+        <v>367</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D190" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E190" t="s" s="0">
         <v>11</v>
@@ -6293,16 +6308,16 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
-        <v>300</v>
+        <v>369</v>
       </c>
       <c r="B191" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C191" t="s" s="0">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D191" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s" s="0">
         <v>11</v>
@@ -6316,16 +6331,16 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="D192" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E192" t="s" s="0">
         <v>11</v>
@@ -6339,22 +6354,22 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>304</v>
+        <v>373</v>
       </c>
       <c r="B193" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C193" t="s" s="0">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D193" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E193" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F193" t="n" s="0">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G193" t="s" s="0">
         <v>12</v>
@@ -6362,22 +6377,22 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="0">
-        <v>306</v>
+        <v>375</v>
       </c>
       <c r="B194" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C194" t="s" s="0">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="D194" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E194" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F194" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="G194" t="s" s="0">
         <v>12</v>
@@ -6385,22 +6400,22 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="0">
-        <v>308</v>
+        <v>377</v>
       </c>
       <c r="B195" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C195" t="s" s="0">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D195" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E195" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F195" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G195" t="s" s="0">
         <v>12</v>
@@ -6408,22 +6423,22 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="0">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="B196" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C196" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D196" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E196" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F196" t="n" s="0">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="G196" t="s" s="0">
         <v>12</v>
@@ -6431,22 +6446,22 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="0">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B197" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C197" t="s" s="0">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D197" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E197" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F197" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G197" t="s" s="0">
         <v>12</v>
@@ -6454,22 +6469,22 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="0">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B198" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C198" t="s" s="0">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="D198" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E198" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F198" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G198" t="s" s="0">
         <v>12</v>
@@ -6477,22 +6492,22 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="0">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B199" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C199" t="s" s="0">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D199" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E199" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F199" t="n" s="0">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G199" t="s" s="0">
         <v>12</v>
@@ -6500,22 +6515,22 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="0">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B200" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C200" t="s" s="0">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D200" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F200" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G200" t="s" s="0">
         <v>12</v>
@@ -6523,22 +6538,22 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B201" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C201" t="s" s="0">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="D201" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E201" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F201" t="n" s="0">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="G201" t="s" s="0">
         <v>12</v>
@@ -6546,22 +6561,22 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="0">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B202" t="s" s="0">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="C202" t="s" s="0">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D202" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F202" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G202" t="s" s="0">
         <v>12</v>
@@ -6569,22 +6584,22 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="0">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B203" t="s" s="0">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="C203" t="s" s="0">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D203" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E203" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F203" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="G203" t="s" s="0">
         <v>12</v>
@@ -6592,22 +6607,22 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="0">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B204" t="s" s="0">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="C204" t="s" s="0">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D204" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E204" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F204" t="n" s="0">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G204" t="s" s="0">
         <v>12</v>
@@ -6615,22 +6630,22 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="0">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B205" t="s" s="0">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="C205" t="s" s="0">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D205" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E205" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F205" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G205" t="s" s="0">
         <v>12</v>
@@ -6638,22 +6653,22 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="0">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B206" t="s" s="0">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="C206" t="s" s="0">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D206" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F206" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="G206" t="s" s="0">
         <v>12</v>
@@ -6661,22 +6676,22 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="0">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B207" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C207" t="s" s="0">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D207" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E207" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F207" t="n" s="0">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
       <c r="G207" t="s" s="0">
         <v>12</v>
@@ -6684,22 +6699,22 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="0">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B208" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C208" t="s" s="0">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="D208" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F208" t="n" s="0">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="G208" t="s" s="0">
         <v>12</v>
@@ -6707,22 +6722,22 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="0">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B209" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C209" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D209" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E209" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F209" t="n" s="0">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G209" t="s" s="0">
         <v>12</v>
@@ -6730,16 +6745,16 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="0">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B210" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C210" t="s" s="0">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="D210" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E210" t="s" s="0">
         <v>11</v>
@@ -6753,22 +6768,22 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="0">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B211" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C211" t="s" s="0">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="D211" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E211" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F211" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G211" t="s" s="0">
         <v>12</v>
@@ -6776,22 +6791,22 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="0">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B212" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C212" t="s" s="0">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D212" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E212" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F212" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="G212" t="s" s="0">
         <v>12</v>
@@ -6799,22 +6814,22 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="0">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B213" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C213" t="s" s="0">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D213" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E213" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F213" t="n" s="0">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="G213" t="s" s="0">
         <v>12</v>
@@ -6822,16 +6837,16 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="0">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B214" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C214" t="s" s="0">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D214" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E214" t="s" s="0">
         <v>11</v>
@@ -6845,22 +6860,22 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="0">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B215" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C215" t="s" s="0">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D215" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E215" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F215" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G215" t="s" s="0">
         <v>12</v>
@@ -6868,22 +6883,22 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="0">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B216" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C216" t="s" s="0">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D216" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E216" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F216" t="n" s="0">
-        <v>26.0</v>
+        <v>16.0</v>
       </c>
       <c r="G216" t="s" s="0">
         <v>12</v>
@@ -6891,22 +6906,22 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="0">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B217" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C217" t="s" s="0">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="D217" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E217" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F217" t="n" s="0">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="G217" t="s" s="0">
         <v>12</v>
@@ -6914,22 +6929,22 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="0">
+        <v>425</v>
+      </c>
+      <c r="B218" t="s" s="0">
         <v>413</v>
       </c>
-      <c r="B218" t="s" s="0">
-        <v>391</v>
-      </c>
       <c r="C218" t="s" s="0">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="D218" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E218" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F218" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G218" t="s" s="0">
         <v>12</v>
@@ -6937,16 +6952,16 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="0">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B219" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C219" t="s" s="0">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="D219" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E219" t="s" s="0">
         <v>11</v>
@@ -6960,22 +6975,22 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="0">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B220" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C220" t="s" s="0">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D220" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E220" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F220" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G220" t="s" s="0">
         <v>12</v>
@@ -6983,16 +6998,16 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="0">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B221" t="s" s="0">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C221" t="s" s="0">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D221" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E221" t="s" s="0">
         <v>11</v>
@@ -7006,22 +7021,22 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="0">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B222" t="s" s="0">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C222" t="s" s="0">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D222" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E222" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F222" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="G222" t="s" s="0">
         <v>12</v>
@@ -7029,22 +7044,22 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="0">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B223" t="s" s="0">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C223" t="s" s="0">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D223" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E223" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F223" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="G223" t="s" s="0">
         <v>12</v>
@@ -7052,22 +7067,22 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="0">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B224" t="s" s="0">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C224" t="s" s="0">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D224" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E224" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F224" t="n" s="0">
-        <v>13.0</v>
+        <v>23.0</v>
       </c>
       <c r="G224" t="s" s="0">
         <v>12</v>
@@ -7075,22 +7090,22 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="0">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B225" t="s" s="0">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C225" t="s" s="0">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D225" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E225" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F225" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G225" t="s" s="0">
         <v>12</v>
@@ -7098,22 +7113,22 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="0">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B226" t="s" s="0">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C226" t="s" s="0">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D226" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E226" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F226" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G226" t="s" s="0">
         <v>12</v>
@@ -7121,16 +7136,16 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="0">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B227" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C227" t="s" s="0">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D227" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E227" t="s" s="0">
         <v>11</v>
@@ -7144,16 +7159,16 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="0">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B228" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C228" t="s" s="0">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D228" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E228" t="s" s="0">
         <v>11</v>
@@ -7167,22 +7182,22 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="0">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B229" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C229" t="s" s="0">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D229" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E229" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F229" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G229" t="s" s="0">
         <v>12</v>
@@ -7190,16 +7205,16 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="0">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B230" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C230" t="s" s="0">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="D230" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E230" t="s" s="0">
         <v>11</v>
@@ -7213,22 +7228,22 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="0">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B231" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C231" t="s" s="0">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D231" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E231" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F231" t="n" s="0">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G231" t="s" s="0">
         <v>12</v>
@@ -7236,22 +7251,22 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="0">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B232" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C232" t="s" s="0">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D232" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E232" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F232" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G232" t="s" s="0">
         <v>12</v>
@@ -7259,22 +7274,22 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="B233" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="B233" t="s" s="0">
-        <v>422</v>
-      </c>
       <c r="C233" t="s" s="0">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="D233" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F233" t="n" s="0">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="G233" t="s" s="0">
         <v>12</v>
@@ -7282,22 +7297,22 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="0">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B234" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C234" t="s" s="0">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D234" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E234" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F234" t="n" s="0">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="G234" t="s" s="0">
         <v>12</v>
@@ -7305,22 +7320,22 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="0">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B235" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C235" t="s" s="0">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="D235" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E235" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F235" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G235" t="s" s="0">
         <v>12</v>
@@ -7328,22 +7343,22 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="0">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B236" t="s" s="0">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C236" t="s" s="0">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D236" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E236" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F236" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G236" t="s" s="0">
         <v>12</v>
@@ -7351,16 +7366,16 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="0">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B237" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C237" t="s" s="0">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D237" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E237" t="s" s="0">
         <v>11</v>
@@ -7374,16 +7389,16 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="0">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B238" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C238" t="s" s="0">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="D238" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E238" t="s" s="0">
         <v>11</v>
@@ -7397,22 +7412,22 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="0">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B239" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C239" t="s" s="0">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="D239" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E239" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F239" t="n" s="0">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
       <c r="G239" t="s" s="0">
         <v>12</v>
@@ -7420,22 +7435,22 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="0">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B240" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C240" t="s" s="0">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="D240" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E240" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F240" t="n" s="0">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G240" t="s" s="0">
         <v>12</v>
@@ -7443,22 +7458,22 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="0">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B241" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C241" t="s" s="0">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D241" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E241" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F241" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G241" t="s" s="0">
         <v>12</v>
@@ -7466,22 +7481,22 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="0">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B242" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C242" t="s" s="0">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D242" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E242" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F242" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G242" t="s" s="0">
         <v>12</v>
@@ -7489,16 +7504,16 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="0">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B243" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C243" t="s" s="0">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D243" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E243" t="s" s="0">
         <v>11</v>
@@ -7512,22 +7527,22 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="0">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B244" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C244" t="s" s="0">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D244" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E244" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F244" t="n" s="0">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
       <c r="G244" t="s" s="0">
         <v>12</v>
@@ -7535,22 +7550,22 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="0">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B245" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C245" t="s" s="0">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D245" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F245" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G245" t="s" s="0">
         <v>12</v>
@@ -7558,22 +7573,22 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="0">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B246" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C246" t="s" s="0">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D246" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E246" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F246" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G246" t="s" s="0">
         <v>12</v>
@@ -7581,16 +7596,16 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="0">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B247" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C247" t="s" s="0">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D247" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E247" t="s" s="0">
         <v>11</v>
@@ -7604,22 +7619,22 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="0">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B248" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C248" t="s" s="0">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="D248" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E248" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F248" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G248" t="s" s="0">
         <v>12</v>
@@ -7627,22 +7642,22 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="0">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B249" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C249" t="s" s="0">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="D249" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E249" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F249" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G249" t="s" s="0">
         <v>12</v>
@@ -7650,22 +7665,22 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="0">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B250" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C250" t="s" s="0">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="D250" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E250" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F250" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G250" t="s" s="0">
         <v>12</v>
@@ -7673,22 +7688,22 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="0">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B251" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C251" t="s" s="0">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D251" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E251" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F251" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="G251" t="s" s="0">
         <v>12</v>
@@ -7696,22 +7711,22 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="0">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B252" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C252" t="s" s="0">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="D252" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E252" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F252" t="n" s="0">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="G252" t="s" s="0">
         <v>12</v>
@@ -7719,22 +7734,22 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="0">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B253" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C253" t="s" s="0">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="D253" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E253" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F253" t="n" s="0">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
       <c r="G253" t="s" s="0">
         <v>12</v>
@@ -7742,16 +7757,16 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="0">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B254" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C254" t="s" s="0">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="D254" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E254" t="s" s="0">
         <v>11</v>
@@ -7765,22 +7780,22 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="0">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B255" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C255" t="s" s="0">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="D255" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E255" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F255" t="n" s="0">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="G255" t="s" s="0">
         <v>12</v>
@@ -7788,16 +7803,16 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="0">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B256" t="s" s="0">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C256" t="s" s="0">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="D256" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E256" t="s" s="0">
         <v>11</v>
@@ -7811,22 +7826,22 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="0">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B257" t="s" s="0">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C257" t="s" s="0">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="D257" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E257" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F257" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G257" t="s" s="0">
         <v>12</v>
@@ -7834,22 +7849,22 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="0">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B258" t="s" s="0">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C258" t="s" s="0">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="D258" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E258" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F258" t="n" s="0">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="G258" t="s" s="0">
         <v>12</v>
@@ -7857,16 +7872,16 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="0">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B259" t="s" s="0">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C259" t="s" s="0">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D259" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E259" t="s" s="0">
         <v>11</v>
@@ -7880,22 +7895,22 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="0">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B260" t="s" s="0">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C260" t="s" s="0">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="D260" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E260" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F260" t="n" s="0">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
       <c r="G260" t="s" s="0">
         <v>12</v>
@@ -7903,22 +7918,22 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="0">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B261" t="s" s="0">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C261" t="s" s="0">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D261" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E261" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F261" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G261" t="s" s="0">
         <v>12</v>
@@ -7926,22 +7941,22 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="0">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B262" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C262" t="s" s="0">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D262" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E262" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F262" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G262" t="s" s="0">
         <v>12</v>
@@ -7949,16 +7964,16 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="0">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B263" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C263" t="s" s="0">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="D263" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E263" t="s" s="0">
         <v>11</v>
@@ -7972,22 +7987,22 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="0">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B264" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C264" t="s" s="0">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="D264" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E264" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F264" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G264" t="s" s="0">
         <v>12</v>
@@ -7995,22 +8010,22 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="0">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B265" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C265" t="s" s="0">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D265" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E265" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F265" t="n" s="0">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="G265" t="s" s="0">
         <v>12</v>
@@ -8018,22 +8033,22 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="0">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B266" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C266" t="s" s="0">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="D266" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E266" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F266" t="n" s="0">
-        <v>24.0</v>
+        <v>15.0</v>
       </c>
       <c r="G266" t="s" s="0">
         <v>12</v>
@@ -8041,22 +8056,22 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="0">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B267" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C267" t="s" s="0">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="D267" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E267" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F267" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G267" t="s" s="0">
         <v>12</v>
@@ -8064,22 +8079,22 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="0">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="B268" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C268" t="s" s="0">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="D268" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E268" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F268" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G268" t="s" s="0">
         <v>12</v>
@@ -8087,22 +8102,22 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="0">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B269" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C269" t="s" s="0">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="D269" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E269" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F269" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G269" t="s" s="0">
         <v>12</v>
@@ -8110,16 +8125,16 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="0">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B270" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C270" t="s" s="0">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="D270" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E270" t="s" s="0">
         <v>11</v>
@@ -8133,16 +8148,16 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="0">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="B271" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C271" t="s" s="0">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D271" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E271" t="s" s="0">
         <v>11</v>
@@ -8156,22 +8171,22 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="0">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="B272" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C272" t="s" s="0">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="D272" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E272" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F272" t="n" s="0">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G272" t="s" s="0">
         <v>12</v>
@@ -8179,16 +8194,16 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="0">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="B273" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C273" t="s" s="0">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="D273" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E273" t="s" s="0">
         <v>11</v>
@@ -8202,22 +8217,22 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="0">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="B274" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C274" t="s" s="0">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D274" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E274" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F274" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G274" t="s" s="0">
         <v>12</v>
@@ -8225,22 +8240,22 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="0">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="B275" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C275" t="s" s="0">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="D275" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E275" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F275" t="n" s="0">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
       <c r="G275" t="s" s="0">
         <v>12</v>
@@ -8248,22 +8263,22 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="0">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B276" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C276" t="s" s="0">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="D276" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E276" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F276" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G276" t="s" s="0">
         <v>12</v>
@@ -8271,22 +8286,22 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="0">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="B277" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C277" t="s" s="0">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="D277" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E277" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F277" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G277" t="s" s="0">
         <v>12</v>
@@ -8294,22 +8309,22 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="0">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="B278" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C278" t="s" s="0">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D278" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E278" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F278" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G278" t="s" s="0">
         <v>12</v>
@@ -8317,22 +8332,22 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="0">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="B279" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C279" t="s" s="0">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="D279" t="s" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E279" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F279" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G279" t="s" s="0">
         <v>12</v>
@@ -8340,22 +8355,22 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="0">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="B280" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C280" t="s" s="0">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="D280" t="s" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E280" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F280" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G280" t="s" s="0">
         <v>12</v>
@@ -8363,16 +8378,16 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="0">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="B281" t="s" s="0">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C281" t="s" s="0">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="D281" t="s" s="0">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E281" t="s" s="0">
         <v>11</v>
@@ -8386,13 +8401,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="0">
-        <v>105</v>
+        <v>555</v>
       </c>
       <c r="B282" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C282" t="s" s="0">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="D282" t="s" s="0">
         <v>10</v>
@@ -8409,13 +8424,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="0">
-        <v>108</v>
+        <v>558</v>
       </c>
       <c r="B283" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C283" t="s" s="0">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D283" t="s" s="0">
         <v>15</v>
@@ -8424,7 +8439,7 @@
         <v>11</v>
       </c>
       <c r="F283" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G283" t="s" s="0">
         <v>12</v>
@@ -8432,13 +8447,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="0">
-        <v>110</v>
+        <v>560</v>
       </c>
       <c r="B284" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C284" t="s" s="0">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="D284" t="s" s="0">
         <v>18</v>
@@ -8455,13 +8470,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="0">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="B285" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C285" t="s" s="0">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="D285" t="s" s="0">
         <v>10</v>
@@ -8470,7 +8485,7 @@
         <v>11</v>
       </c>
       <c r="F285" t="n" s="0">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G285" t="s" s="0">
         <v>12</v>
@@ -8478,13 +8493,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="0">
-        <v>114</v>
+        <v>564</v>
       </c>
       <c r="B286" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C286" t="s" s="0">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="D286" t="s" s="0">
         <v>15</v>
@@ -8501,13 +8516,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="0">
-        <v>116</v>
+        <v>566</v>
       </c>
       <c r="B287" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C287" t="s" s="0">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="D287" t="s" s="0">
         <v>18</v>
@@ -8524,13 +8539,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="0">
-        <v>118</v>
+        <v>568</v>
       </c>
       <c r="B288" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C288" t="s" s="0">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="D288" t="s" s="0">
         <v>10</v>
@@ -8539,7 +8554,7 @@
         <v>11</v>
       </c>
       <c r="F288" t="n" s="0">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="G288" t="s" s="0">
         <v>12</v>
@@ -8547,13 +8562,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="0">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="B289" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C289" t="s" s="0">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="D289" t="s" s="0">
         <v>15</v>
@@ -8570,13 +8585,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="0">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="B290" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C290" t="s" s="0">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="D290" t="s" s="0">
         <v>18</v>
@@ -8593,13 +8608,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="0">
-        <v>124</v>
+        <v>574</v>
       </c>
       <c r="B291" t="s" s="0">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="C291" t="s" s="0">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="D291" t="s" s="0">
         <v>10</v>
@@ -8608,7 +8623,7 @@
         <v>11</v>
       </c>
       <c r="F291" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G291" t="s" s="0">
         <v>12</v>
@@ -8616,16 +8631,16 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="0">
-        <v>126</v>
+        <v>576</v>
       </c>
       <c r="B292" t="s" s="0">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C292" t="s" s="0">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="D292" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E292" t="s" s="0">
         <v>11</v>
@@ -8639,16 +8654,16 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="0">
-        <v>128</v>
+        <v>579</v>
       </c>
       <c r="B293" t="s" s="0">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C293" t="s" s="0">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="D293" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E293" t="s" s="0">
         <v>11</v>
@@ -8662,22 +8677,22 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="0">
-        <v>130</v>
+        <v>581</v>
       </c>
       <c r="B294" t="s" s="0">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C294" t="s" s="0">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="D294" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E294" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F294" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="G294" t="s" s="0">
         <v>12</v>
@@ -8685,16 +8700,16 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="0">
-        <v>132</v>
+        <v>583</v>
       </c>
       <c r="B295" t="s" s="0">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C295" t="s" s="0">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="D295" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s" s="0">
         <v>11</v>
@@ -8708,22 +8723,22 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="0">
-        <v>134</v>
+        <v>585</v>
       </c>
       <c r="B296" t="s" s="0">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C296" t="s" s="0">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="D296" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E296" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F296" t="n" s="0">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="G296" t="s" s="0">
         <v>12</v>
@@ -8731,22 +8746,22 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="0">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="B297" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C297" t="s" s="0">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="D297" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E297" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F297" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G297" t="s" s="0">
         <v>12</v>
@@ -8754,16 +8769,16 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="0">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="B298" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C298" t="s" s="0">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="D298" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E298" t="s" s="0">
         <v>11</v>
@@ -8777,22 +8792,22 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="0">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="B299" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C299" t="s" s="0">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="D299" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E299" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F299" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G299" t="s" s="0">
         <v>12</v>
@@ -8800,16 +8815,16 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="0">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="B300" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C300" t="s" s="0">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="D300" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E300" t="s" s="0">
         <v>11</v>
@@ -8823,22 +8838,22 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="0">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="B301" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C301" t="s" s="0">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="D301" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E301" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F301" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G301" t="s" s="0">
         <v>12</v>
@@ -8846,22 +8861,22 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="0">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="B302" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C302" t="s" s="0">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="D302" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E302" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F302" t="n" s="0">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="G302" t="s" s="0">
         <v>12</v>
@@ -8869,16 +8884,16 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="0">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B303" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C303" t="s" s="0">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="D303" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E303" t="s" s="0">
         <v>11</v>
@@ -8892,16 +8907,16 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="0">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="B304" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C304" t="s" s="0">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="D304" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E304" t="s" s="0">
         <v>11</v>
@@ -8915,22 +8930,22 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="0">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B305" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C305" t="s" s="0">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="D305" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E305" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F305" t="n" s="0">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="G305" t="s" s="0">
         <v>12</v>
@@ -8938,22 +8953,22 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="0">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="B306" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C306" t="s" s="0">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="D306" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E306" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F306" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G306" t="s" s="0">
         <v>12</v>
@@ -8961,22 +8976,22 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="0">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="B307" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C307" t="s" s="0">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="D307" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E307" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F307" t="n" s="0">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="G307" t="s" s="0">
         <v>12</v>
@@ -8984,22 +8999,22 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="0">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="B308" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C308" t="s" s="0">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="D308" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E308" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F308" t="n" s="0">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G308" t="s" s="0">
         <v>12</v>
@@ -9007,22 +9022,22 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="0">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="B309" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C309" t="s" s="0">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="D309" t="s" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E309" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F309" t="n" s="0">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="G309" t="s" s="0">
         <v>12</v>
@@ -9030,22 +9045,22 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="0">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="B310" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C310" t="s" s="0">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="D310" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F310" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G310" t="s" s="0">
         <v>12</v>
@@ -9053,254 +9068,24 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="0">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B311" t="s" s="0">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C311" t="s" s="0">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="D311" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E311" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F311" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G311" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="s" s="0">
-        <v>592</v>
-      </c>
-      <c r="B312" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C312" t="s" s="0">
-        <v>593</v>
-      </c>
-      <c r="D312" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E312" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F312" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="G312" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="s" s="0">
-        <v>594</v>
-      </c>
-      <c r="B313" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C313" t="s" s="0">
-        <v>595</v>
-      </c>
-      <c r="D313" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E313" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F313" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="G313" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="s" s="0">
-        <v>596</v>
-      </c>
-      <c r="B314" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C314" t="s" s="0">
-        <v>597</v>
-      </c>
-      <c r="D314" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E314" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F314" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="G314" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="B315" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C315" t="s" s="0">
-        <v>599</v>
-      </c>
-      <c r="D315" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E315" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F315" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="G315" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="s" s="0">
-        <v>600</v>
-      </c>
-      <c r="B316" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C316" t="s" s="0">
-        <v>601</v>
-      </c>
-      <c r="D316" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E316" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F316" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="G316" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="B317" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C317" t="s" s="0">
-        <v>603</v>
-      </c>
-      <c r="D317" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E317" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F317" t="n" s="0">
-        <v>18.0</v>
-      </c>
-      <c r="G317" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="s" s="0">
-        <v>604</v>
-      </c>
-      <c r="B318" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C318" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="D318" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E318" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F318" t="n" s="0">
-        <v>11.0</v>
-      </c>
-      <c r="G318" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="s" s="0">
-        <v>606</v>
-      </c>
-      <c r="B319" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C319" t="s" s="0">
-        <v>607</v>
-      </c>
-      <c r="D319" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E319" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F319" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="G319" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="s" s="0">
-        <v>608</v>
-      </c>
-      <c r="B320" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C320" t="s" s="0">
-        <v>609</v>
-      </c>
-      <c r="D320" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E320" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F320" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="G320" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="B321" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="C321" t="s" s="0">
-        <v>611</v>
-      </c>
-      <c r="D321" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E321" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F321" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="G321" t="s" s="0">
         <v>12</v>
       </c>
     </row>

--- a/automation/reports/Excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Passed_Test_Cases.xlsx
@@ -1991,7 +1991,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>30.0</v>
+        <v>16.0</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>12</v>
@@ -2014,7 +2014,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>14.0</v>
+        <v>29.0</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>12</v>
@@ -2106,7 +2106,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>12</v>
@@ -2129,7 +2129,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>12</v>
@@ -2175,7 +2175,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>12</v>
@@ -2198,7 +2198,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>12</v>
@@ -2221,7 +2221,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>12</v>
@@ -2244,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>12</v>
@@ -2267,7 +2267,7 @@
         <v>11</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>12</v>
@@ -2290,7 +2290,7 @@
         <v>11</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>12</v>
@@ -2313,7 +2313,7 @@
         <v>11</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>12</v>
@@ -2382,7 +2382,7 @@
         <v>11</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>12</v>
@@ -2428,7 +2428,7 @@
         <v>11</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>12</v>
@@ -2474,7 +2474,7 @@
         <v>11</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>12</v>
@@ -2497,7 +2497,7 @@
         <v>11</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>12</v>
@@ -2520,7 +2520,7 @@
         <v>11</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>12</v>
@@ -2543,7 +2543,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>12</v>
@@ -2566,7 +2566,7 @@
         <v>11</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>12</v>
@@ -2612,7 +2612,7 @@
         <v>11</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>12</v>
@@ -2635,7 +2635,7 @@
         <v>11</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>12</v>
@@ -2658,7 +2658,7 @@
         <v>11</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>12</v>
@@ -2704,7 +2704,7 @@
         <v>11</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>12</v>
@@ -2727,7 +2727,7 @@
         <v>11</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>12</v>
@@ -2773,7 +2773,7 @@
         <v>11</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>12</v>
@@ -2796,7 +2796,7 @@
         <v>11</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>12</v>
@@ -2819,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="F38" t="n" s="0">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>12</v>
@@ -2842,7 +2842,7 @@
         <v>11</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>12</v>
@@ -2865,7 +2865,7 @@
         <v>11</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>12</v>
@@ -2888,7 +2888,7 @@
         <v>11</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>26.0</v>
+        <v>16.0</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>12</v>
@@ -2911,7 +2911,7 @@
         <v>11</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
       <c r="G42" t="s" s="0">
         <v>12</v>
@@ -2934,7 +2934,7 @@
         <v>11</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G43" t="s" s="0">
         <v>12</v>
@@ -2957,7 +2957,7 @@
         <v>11</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="G44" t="s" s="0">
         <v>12</v>
@@ -2980,7 +2980,7 @@
         <v>11</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>25.0</v>
+        <v>14.0</v>
       </c>
       <c r="G45" t="s" s="0">
         <v>12</v>
@@ -3026,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="G47" t="s" s="0">
         <v>12</v>
@@ -3049,7 +3049,7 @@
         <v>11</v>
       </c>
       <c r="F48" t="n" s="0">
-        <v>16.0</v>
+        <v>27.0</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>12</v>
@@ -3072,7 +3072,7 @@
         <v>11</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>12</v>
@@ -3095,7 +3095,7 @@
         <v>11</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>12</v>
@@ -3118,7 +3118,7 @@
         <v>11</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>12</v>
@@ -3187,7 +3187,7 @@
         <v>11</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G54" t="s" s="0">
         <v>12</v>
@@ -3210,7 +3210,7 @@
         <v>11</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G55" t="s" s="0">
         <v>12</v>
@@ -3233,7 +3233,7 @@
         <v>11</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
       <c r="G56" t="s" s="0">
         <v>12</v>
@@ -3256,7 +3256,7 @@
         <v>11</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G57" t="s" s="0">
         <v>12</v>
@@ -3279,7 +3279,7 @@
         <v>11</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G58" t="s" s="0">
         <v>12</v>
@@ -3325,7 +3325,7 @@
         <v>11</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G60" t="s" s="0">
         <v>12</v>
@@ -3348,7 +3348,7 @@
         <v>11</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="G61" t="s" s="0">
         <v>12</v>
@@ -3371,7 +3371,7 @@
         <v>11</v>
       </c>
       <c r="F62" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G62" t="s" s="0">
         <v>12</v>
@@ -3394,7 +3394,7 @@
         <v>11</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G63" t="s" s="0">
         <v>12</v>
@@ -3417,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G64" t="s" s="0">
         <v>12</v>
@@ -3440,7 +3440,7 @@
         <v>11</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G65" t="s" s="0">
         <v>12</v>
@@ -3463,7 +3463,7 @@
         <v>11</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G66" t="s" s="0">
         <v>12</v>
@@ -3486,7 +3486,7 @@
         <v>11</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G67" t="s" s="0">
         <v>12</v>
@@ -3509,7 +3509,7 @@
         <v>11</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>23.0</v>
+        <v>15.0</v>
       </c>
       <c r="G68" t="s" s="0">
         <v>12</v>
@@ -3532,7 +3532,7 @@
         <v>11</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="G69" t="s" s="0">
         <v>12</v>
@@ -3555,7 +3555,7 @@
         <v>11</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G70" t="s" s="0">
         <v>12</v>
@@ -3578,7 +3578,7 @@
         <v>11</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G71" t="s" s="0">
         <v>12</v>
@@ -3601,7 +3601,7 @@
         <v>11</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G72" t="s" s="0">
         <v>12</v>
@@ -3647,7 +3647,7 @@
         <v>11</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G74" t="s" s="0">
         <v>12</v>
@@ -3670,7 +3670,7 @@
         <v>11</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G75" t="s" s="0">
         <v>12</v>
@@ -3693,7 +3693,7 @@
         <v>11</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G76" t="s" s="0">
         <v>12</v>
@@ -3716,7 +3716,7 @@
         <v>11</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G77" t="s" s="0">
         <v>12</v>
@@ -3739,7 +3739,7 @@
         <v>11</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G78" t="s" s="0">
         <v>12</v>
@@ -3762,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="G79" t="s" s="0">
         <v>12</v>
@@ -3785,7 +3785,7 @@
         <v>11</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="G80" t="s" s="0">
         <v>12</v>
@@ -3831,7 +3831,7 @@
         <v>11</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="G82" t="s" s="0">
         <v>12</v>
@@ -3854,7 +3854,7 @@
         <v>11</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G83" t="s" s="0">
         <v>12</v>
@@ -3877,7 +3877,7 @@
         <v>11</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G84" t="s" s="0">
         <v>12</v>
@@ -3900,7 +3900,7 @@
         <v>11</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="G85" t="s" s="0">
         <v>12</v>
@@ -3923,7 +3923,7 @@
         <v>11</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G86" t="s" s="0">
         <v>12</v>
@@ -3946,7 +3946,7 @@
         <v>11</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G87" t="s" s="0">
         <v>12</v>
@@ -4015,7 +4015,7 @@
         <v>11</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G90" t="s" s="0">
         <v>12</v>
@@ -4061,7 +4061,7 @@
         <v>11</v>
       </c>
       <c r="F92" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G92" t="s" s="0">
         <v>12</v>
@@ -4084,7 +4084,7 @@
         <v>11</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G93" t="s" s="0">
         <v>12</v>
@@ -4130,7 +4130,7 @@
         <v>11</v>
       </c>
       <c r="F95" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G95" t="s" s="0">
         <v>12</v>
@@ -4153,7 +4153,7 @@
         <v>11</v>
       </c>
       <c r="F96" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G96" t="s" s="0">
         <v>12</v>
@@ -4176,7 +4176,7 @@
         <v>11</v>
       </c>
       <c r="F97" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G97" t="s" s="0">
         <v>12</v>
@@ -4222,7 +4222,7 @@
         <v>11</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G99" t="s" s="0">
         <v>12</v>
@@ -4245,7 +4245,7 @@
         <v>11</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G100" t="s" s="0">
         <v>12</v>
@@ -4360,7 +4360,7 @@
         <v>11</v>
       </c>
       <c r="F105" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G105" t="s" s="0">
         <v>12</v>
@@ -4406,7 +4406,7 @@
         <v>11</v>
       </c>
       <c r="F107" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G107" t="s" s="0">
         <v>12</v>
@@ -4429,7 +4429,7 @@
         <v>11</v>
       </c>
       <c r="F108" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G108" t="s" s="0">
         <v>12</v>
@@ -4452,7 +4452,7 @@
         <v>11</v>
       </c>
       <c r="F109" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G109" t="s" s="0">
         <v>12</v>
@@ -4498,7 +4498,7 @@
         <v>11</v>
       </c>
       <c r="F111" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G111" t="s" s="0">
         <v>12</v>
@@ -4521,7 +4521,7 @@
         <v>11</v>
       </c>
       <c r="F112" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G112" t="s" s="0">
         <v>12</v>
@@ -4544,7 +4544,7 @@
         <v>11</v>
       </c>
       <c r="F113" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>12</v>
@@ -4567,7 +4567,7 @@
         <v>11</v>
       </c>
       <c r="F114" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>12</v>
@@ -4590,7 +4590,7 @@
         <v>11</v>
       </c>
       <c r="F115" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>12</v>
@@ -4613,7 +4613,7 @@
         <v>11</v>
       </c>
       <c r="F116" t="n" s="0">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="G116" t="s" s="0">
         <v>12</v>
@@ -4636,7 +4636,7 @@
         <v>11</v>
       </c>
       <c r="F117" t="n" s="0">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="G117" t="s" s="0">
         <v>12</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="F118" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G118" t="s" s="0">
         <v>12</v>
@@ -4682,7 +4682,7 @@
         <v>11</v>
       </c>
       <c r="F119" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G119" t="s" s="0">
         <v>12</v>
@@ -4728,7 +4728,7 @@
         <v>11</v>
       </c>
       <c r="F121" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>12</v>
@@ -4751,7 +4751,7 @@
         <v>11</v>
       </c>
       <c r="F122" t="n" s="0">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="G122" t="s" s="0">
         <v>12</v>
@@ -4774,7 +4774,7 @@
         <v>11</v>
       </c>
       <c r="F123" t="n" s="0">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>12</v>
@@ -4797,7 +4797,7 @@
         <v>11</v>
       </c>
       <c r="F124" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G124" t="s" s="0">
         <v>12</v>
@@ -4820,7 +4820,7 @@
         <v>11</v>
       </c>
       <c r="F125" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G125" t="s" s="0">
         <v>12</v>
@@ -4843,7 +4843,7 @@
         <v>11</v>
       </c>
       <c r="F126" t="n" s="0">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G126" t="s" s="0">
         <v>12</v>
@@ -4866,7 +4866,7 @@
         <v>11</v>
       </c>
       <c r="F127" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G127" t="s" s="0">
         <v>12</v>
@@ -4889,7 +4889,7 @@
         <v>11</v>
       </c>
       <c r="F128" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G128" t="s" s="0">
         <v>12</v>
@@ -4912,7 +4912,7 @@
         <v>11</v>
       </c>
       <c r="F129" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G129" t="s" s="0">
         <v>12</v>
@@ -4958,7 +4958,7 @@
         <v>11</v>
       </c>
       <c r="F131" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G131" t="s" s="0">
         <v>12</v>
@@ -4981,7 +4981,7 @@
         <v>11</v>
       </c>
       <c r="F132" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G132" t="s" s="0">
         <v>12</v>
@@ -5004,7 +5004,7 @@
         <v>11</v>
       </c>
       <c r="F133" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G133" t="s" s="0">
         <v>12</v>
@@ -5027,7 +5027,7 @@
         <v>11</v>
       </c>
       <c r="F134" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G134" t="s" s="0">
         <v>12</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="F135" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="G135" t="s" s="0">
         <v>12</v>
@@ -5073,7 +5073,7 @@
         <v>11</v>
       </c>
       <c r="F136" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G136" t="s" s="0">
         <v>12</v>
@@ -5119,7 +5119,7 @@
         <v>11</v>
       </c>
       <c r="F138" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G138" t="s" s="0">
         <v>12</v>
@@ -5142,7 +5142,7 @@
         <v>11</v>
       </c>
       <c r="F139" t="n" s="0">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="G139" t="s" s="0">
         <v>12</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="F140" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G140" t="s" s="0">
         <v>12</v>
@@ -5188,7 +5188,7 @@
         <v>11</v>
       </c>
       <c r="F141" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G141" t="s" s="0">
         <v>12</v>
@@ -5211,7 +5211,7 @@
         <v>11</v>
       </c>
       <c r="F142" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G142" t="s" s="0">
         <v>12</v>
@@ -5234,7 +5234,7 @@
         <v>11</v>
       </c>
       <c r="F143" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G143" t="s" s="0">
         <v>12</v>
@@ -5257,7 +5257,7 @@
         <v>11</v>
       </c>
       <c r="F144" t="n" s="0">
-        <v>17.0</v>
+        <v>30.0</v>
       </c>
       <c r="G144" t="s" s="0">
         <v>12</v>
@@ -5280,7 +5280,7 @@
         <v>11</v>
       </c>
       <c r="F145" t="n" s="0">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="G145" t="s" s="0">
         <v>12</v>
@@ -5303,7 +5303,7 @@
         <v>11</v>
       </c>
       <c r="F146" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G146" t="s" s="0">
         <v>12</v>
@@ -5326,7 +5326,7 @@
         <v>11</v>
       </c>
       <c r="F147" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G147" t="s" s="0">
         <v>12</v>
@@ -5349,7 +5349,7 @@
         <v>11</v>
       </c>
       <c r="F148" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G148" t="s" s="0">
         <v>12</v>
@@ -5372,7 +5372,7 @@
         <v>11</v>
       </c>
       <c r="F149" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G149" t="s" s="0">
         <v>12</v>
@@ -5395,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="F150" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G150" t="s" s="0">
         <v>12</v>
@@ -5418,7 +5418,7 @@
         <v>11</v>
       </c>
       <c r="F151" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G151" t="s" s="0">
         <v>12</v>
@@ -5441,7 +5441,7 @@
         <v>11</v>
       </c>
       <c r="F152" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G152" t="s" s="0">
         <v>12</v>
@@ -5464,7 +5464,7 @@
         <v>11</v>
       </c>
       <c r="F153" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G153" t="s" s="0">
         <v>12</v>
@@ -5487,7 +5487,7 @@
         <v>11</v>
       </c>
       <c r="F154" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G154" t="s" s="0">
         <v>12</v>
@@ -5510,7 +5510,7 @@
         <v>11</v>
       </c>
       <c r="F155" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G155" t="s" s="0">
         <v>12</v>
@@ -5533,7 +5533,7 @@
         <v>11</v>
       </c>
       <c r="F156" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G156" t="s" s="0">
         <v>12</v>
@@ -5579,7 +5579,7 @@
         <v>11</v>
       </c>
       <c r="F158" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G158" t="s" s="0">
         <v>12</v>
@@ -5602,7 +5602,7 @@
         <v>11</v>
       </c>
       <c r="F159" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G159" t="s" s="0">
         <v>12</v>
@@ -5625,7 +5625,7 @@
         <v>11</v>
       </c>
       <c r="F160" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G160" t="s" s="0">
         <v>12</v>
@@ -5648,7 +5648,7 @@
         <v>11</v>
       </c>
       <c r="F161" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G161" t="s" s="0">
         <v>12</v>
@@ -5671,7 +5671,7 @@
         <v>11</v>
       </c>
       <c r="F162" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G162" t="s" s="0">
         <v>12</v>
@@ -5694,7 +5694,7 @@
         <v>11</v>
       </c>
       <c r="F163" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G163" t="s" s="0">
         <v>12</v>
@@ -5717,7 +5717,7 @@
         <v>11</v>
       </c>
       <c r="F164" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G164" t="s" s="0">
         <v>12</v>
@@ -5740,7 +5740,7 @@
         <v>11</v>
       </c>
       <c r="F165" t="n" s="0">
-        <v>14.0</v>
+        <v>22.0</v>
       </c>
       <c r="G165" t="s" s="0">
         <v>12</v>
@@ -5786,7 +5786,7 @@
         <v>11</v>
       </c>
       <c r="F167" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G167" t="s" s="0">
         <v>12</v>
@@ -5809,7 +5809,7 @@
         <v>11</v>
       </c>
       <c r="F168" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G168" t="s" s="0">
         <v>12</v>
@@ -5832,7 +5832,7 @@
         <v>11</v>
       </c>
       <c r="F169" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G169" t="s" s="0">
         <v>12</v>
@@ -5855,7 +5855,7 @@
         <v>11</v>
       </c>
       <c r="F170" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G170" t="s" s="0">
         <v>12</v>
@@ -5878,7 +5878,7 @@
         <v>11</v>
       </c>
       <c r="F171" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G171" t="s" s="0">
         <v>12</v>
@@ -5901,7 +5901,7 @@
         <v>11</v>
       </c>
       <c r="F172" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G172" t="s" s="0">
         <v>12</v>
@@ -5924,7 +5924,7 @@
         <v>11</v>
       </c>
       <c r="F173" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G173" t="s" s="0">
         <v>12</v>
@@ -5947,7 +5947,7 @@
         <v>11</v>
       </c>
       <c r="F174" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G174" t="s" s="0">
         <v>12</v>
@@ -5970,7 +5970,7 @@
         <v>11</v>
       </c>
       <c r="F175" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G175" t="s" s="0">
         <v>12</v>
@@ -5993,7 +5993,7 @@
         <v>11</v>
       </c>
       <c r="F176" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G176" t="s" s="0">
         <v>12</v>
@@ -6016,7 +6016,7 @@
         <v>11</v>
       </c>
       <c r="F177" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G177" t="s" s="0">
         <v>12</v>
@@ -6039,7 +6039,7 @@
         <v>11</v>
       </c>
       <c r="F178" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G178" t="s" s="0">
         <v>12</v>
@@ -6062,7 +6062,7 @@
         <v>11</v>
       </c>
       <c r="F179" t="n" s="0">
-        <v>18.0</v>
+        <v>30.0</v>
       </c>
       <c r="G179" t="s" s="0">
         <v>12</v>
@@ -6085,7 +6085,7 @@
         <v>11</v>
       </c>
       <c r="F180" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G180" t="s" s="0">
         <v>12</v>
@@ -6108,7 +6108,7 @@
         <v>11</v>
       </c>
       <c r="F181" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G181" t="s" s="0">
         <v>12</v>
@@ -6131,7 +6131,7 @@
         <v>11</v>
       </c>
       <c r="F182" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G182" t="s" s="0">
         <v>12</v>
@@ -6154,7 +6154,7 @@
         <v>11</v>
       </c>
       <c r="F183" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G183" t="s" s="0">
         <v>12</v>
@@ -6177,7 +6177,7 @@
         <v>11</v>
       </c>
       <c r="F184" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G184" t="s" s="0">
         <v>12</v>
@@ -6200,7 +6200,7 @@
         <v>11</v>
       </c>
       <c r="F185" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G185" t="s" s="0">
         <v>12</v>
@@ -6269,7 +6269,7 @@
         <v>11</v>
       </c>
       <c r="F188" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G188" t="s" s="0">
         <v>12</v>
@@ -6292,7 +6292,7 @@
         <v>11</v>
       </c>
       <c r="F189" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G189" t="s" s="0">
         <v>12</v>
@@ -6315,7 +6315,7 @@
         <v>11</v>
       </c>
       <c r="F190" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G190" t="s" s="0">
         <v>12</v>
@@ -6338,7 +6338,7 @@
         <v>11</v>
       </c>
       <c r="F191" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G191" t="s" s="0">
         <v>12</v>
@@ -6384,7 +6384,7 @@
         <v>11</v>
       </c>
       <c r="F193" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G193" t="s" s="0">
         <v>12</v>
@@ -6407,7 +6407,7 @@
         <v>11</v>
       </c>
       <c r="F194" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G194" t="s" s="0">
         <v>12</v>
@@ -6430,7 +6430,7 @@
         <v>11</v>
       </c>
       <c r="F195" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G195" t="s" s="0">
         <v>12</v>
@@ -6476,7 +6476,7 @@
         <v>11</v>
       </c>
       <c r="F197" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G197" t="s" s="0">
         <v>12</v>
@@ -6499,7 +6499,7 @@
         <v>11</v>
       </c>
       <c r="F198" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G198" t="s" s="0">
         <v>12</v>
@@ -6522,7 +6522,7 @@
         <v>11</v>
       </c>
       <c r="F199" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G199" t="s" s="0">
         <v>12</v>
@@ -6545,7 +6545,7 @@
         <v>11</v>
       </c>
       <c r="F200" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G200" t="s" s="0">
         <v>12</v>
@@ -6568,7 +6568,7 @@
         <v>11</v>
       </c>
       <c r="F201" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G201" t="s" s="0">
         <v>12</v>
@@ -6591,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="F202" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G202" t="s" s="0">
         <v>12</v>
@@ -6614,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="F203" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G203" t="s" s="0">
         <v>12</v>
@@ -6660,7 +6660,7 @@
         <v>11</v>
       </c>
       <c r="F205" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G205" t="s" s="0">
         <v>12</v>
@@ -6706,7 +6706,7 @@
         <v>11</v>
       </c>
       <c r="F207" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G207" t="s" s="0">
         <v>12</v>
@@ -6729,7 +6729,7 @@
         <v>11</v>
       </c>
       <c r="F208" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G208" t="s" s="0">
         <v>12</v>
@@ -6752,7 +6752,7 @@
         <v>11</v>
       </c>
       <c r="F209" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G209" t="s" s="0">
         <v>12</v>
@@ -6775,7 +6775,7 @@
         <v>11</v>
       </c>
       <c r="F210" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G210" t="s" s="0">
         <v>12</v>
@@ -6798,7 +6798,7 @@
         <v>11</v>
       </c>
       <c r="F211" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G211" t="s" s="0">
         <v>12</v>
@@ -6821,7 +6821,7 @@
         <v>11</v>
       </c>
       <c r="F212" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G212" t="s" s="0">
         <v>12</v>
@@ -6844,7 +6844,7 @@
         <v>11</v>
       </c>
       <c r="F213" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G213" t="s" s="0">
         <v>12</v>
@@ -6867,7 +6867,7 @@
         <v>11</v>
       </c>
       <c r="F214" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G214" t="s" s="0">
         <v>12</v>
@@ -6913,7 +6913,7 @@
         <v>11</v>
       </c>
       <c r="F216" t="n" s="0">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="G216" t="s" s="0">
         <v>12</v>
@@ -6936,7 +6936,7 @@
         <v>11</v>
       </c>
       <c r="F217" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G217" t="s" s="0">
         <v>12</v>
@@ -6959,7 +6959,7 @@
         <v>11</v>
       </c>
       <c r="F218" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G218" t="s" s="0">
         <v>12</v>
@@ -7005,7 +7005,7 @@
         <v>11</v>
       </c>
       <c r="F220" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G220" t="s" s="0">
         <v>12</v>
@@ -7028,7 +7028,7 @@
         <v>11</v>
       </c>
       <c r="F221" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G221" t="s" s="0">
         <v>12</v>
@@ -7051,7 +7051,7 @@
         <v>11</v>
       </c>
       <c r="F222" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G222" t="s" s="0">
         <v>12</v>
@@ -7097,7 +7097,7 @@
         <v>11</v>
       </c>
       <c r="F224" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G224" t="s" s="0">
         <v>12</v>
@@ -7120,7 +7120,7 @@
         <v>11</v>
       </c>
       <c r="F225" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G225" t="s" s="0">
         <v>12</v>
@@ -7143,7 +7143,7 @@
         <v>11</v>
       </c>
       <c r="F226" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G226" t="s" s="0">
         <v>12</v>
@@ -7166,7 +7166,7 @@
         <v>11</v>
       </c>
       <c r="F227" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G227" t="s" s="0">
         <v>12</v>
@@ -7189,7 +7189,7 @@
         <v>11</v>
       </c>
       <c r="F228" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G228" t="s" s="0">
         <v>12</v>
@@ -7212,7 +7212,7 @@
         <v>11</v>
       </c>
       <c r="F229" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G229" t="s" s="0">
         <v>12</v>
@@ -7235,7 +7235,7 @@
         <v>11</v>
       </c>
       <c r="F230" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G230" t="s" s="0">
         <v>12</v>
@@ -7258,7 +7258,7 @@
         <v>11</v>
       </c>
       <c r="F231" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G231" t="s" s="0">
         <v>12</v>
@@ -7304,7 +7304,7 @@
         <v>11</v>
       </c>
       <c r="F233" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G233" t="s" s="0">
         <v>12</v>
@@ -7327,7 +7327,7 @@
         <v>11</v>
       </c>
       <c r="F234" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G234" t="s" s="0">
         <v>12</v>
@@ -7350,7 +7350,7 @@
         <v>11</v>
       </c>
       <c r="F235" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G235" t="s" s="0">
         <v>12</v>
@@ -7396,7 +7396,7 @@
         <v>11</v>
       </c>
       <c r="F237" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G237" t="s" s="0">
         <v>12</v>
@@ -7419,7 +7419,7 @@
         <v>11</v>
       </c>
       <c r="F238" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G238" t="s" s="0">
         <v>12</v>
@@ -7442,7 +7442,7 @@
         <v>11</v>
       </c>
       <c r="F239" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G239" t="s" s="0">
         <v>12</v>
@@ -7465,7 +7465,7 @@
         <v>11</v>
       </c>
       <c r="F240" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="G240" t="s" s="0">
         <v>12</v>
@@ -7488,7 +7488,7 @@
         <v>11</v>
       </c>
       <c r="F241" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G241" t="s" s="0">
         <v>12</v>
@@ -7511,7 +7511,7 @@
         <v>11</v>
       </c>
       <c r="F242" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G242" t="s" s="0">
         <v>12</v>
@@ -7557,7 +7557,7 @@
         <v>11</v>
       </c>
       <c r="F244" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G244" t="s" s="0">
         <v>12</v>
@@ -7603,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="F246" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G246" t="s" s="0">
         <v>12</v>
@@ -7649,7 +7649,7 @@
         <v>11</v>
       </c>
       <c r="F248" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G248" t="s" s="0">
         <v>12</v>
@@ -7695,7 +7695,7 @@
         <v>11</v>
       </c>
       <c r="F250" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G250" t="s" s="0">
         <v>12</v>
@@ -7718,7 +7718,7 @@
         <v>11</v>
       </c>
       <c r="F251" t="n" s="0">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="G251" t="s" s="0">
         <v>12</v>
@@ -7741,7 +7741,7 @@
         <v>11</v>
       </c>
       <c r="F252" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G252" t="s" s="0">
         <v>12</v>
@@ -7787,7 +7787,7 @@
         <v>11</v>
       </c>
       <c r="F254" t="n" s="0">
-        <v>21.0</v>
+        <v>18.0</v>
       </c>
       <c r="G254" t="s" s="0">
         <v>12</v>
@@ -7833,7 +7833,7 @@
         <v>11</v>
       </c>
       <c r="F256" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G256" t="s" s="0">
         <v>12</v>
@@ -7856,7 +7856,7 @@
         <v>11</v>
       </c>
       <c r="F257" t="n" s="0">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G257" t="s" s="0">
         <v>12</v>
@@ -7879,7 +7879,7 @@
         <v>11</v>
       </c>
       <c r="F258" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G258" t="s" s="0">
         <v>12</v>
@@ -7902,7 +7902,7 @@
         <v>11</v>
       </c>
       <c r="F259" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G259" t="s" s="0">
         <v>12</v>
@@ -7925,7 +7925,7 @@
         <v>11</v>
       </c>
       <c r="F260" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="G260" t="s" s="0">
         <v>12</v>
@@ -7948,7 +7948,7 @@
         <v>11</v>
       </c>
       <c r="F261" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G261" t="s" s="0">
         <v>12</v>
@@ -7971,7 +7971,7 @@
         <v>11</v>
       </c>
       <c r="F262" t="n" s="0">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G262" t="s" s="0">
         <v>12</v>
@@ -7994,7 +7994,7 @@
         <v>11</v>
       </c>
       <c r="F263" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G263" t="s" s="0">
         <v>12</v>
@@ -8017,7 +8017,7 @@
         <v>11</v>
       </c>
       <c r="F264" t="n" s="0">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G264" t="s" s="0">
         <v>12</v>
@@ -8063,7 +8063,7 @@
         <v>11</v>
       </c>
       <c r="F266" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G266" t="s" s="0">
         <v>12</v>
@@ -8086,7 +8086,7 @@
         <v>11</v>
       </c>
       <c r="F267" t="n" s="0">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G267" t="s" s="0">
         <v>12</v>
@@ -8132,7 +8132,7 @@
         <v>11</v>
       </c>
       <c r="F269" t="n" s="0">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="G269" t="s" s="0">
         <v>12</v>
@@ -8201,7 +8201,7 @@
         <v>11</v>
       </c>
       <c r="F272" t="n" s="0">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G272" t="s" s="0">
         <v>12</v>
@@ -8224,7 +8224,7 @@
         <v>11</v>
       </c>
       <c r="F273" t="n" s="0">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="G273" t="s" s="0">
         <v>12</v>
@@ -8247,7 +8247,7 @@
         <v>11</v>
       </c>
       <c r="F274" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G274" t="s" s="0">
         <v>12</v>
@@ -8293,7 +8293,7 @@
         <v>11</v>
       </c>
       <c r="F276" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G276" t="s" s="0">
         <v>12</v>
@@ -8339,7 +8339,7 @@
         <v>11</v>
       </c>
       <c r="F278" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G278" t="s" s="0">
         <v>12</v>
@@ -8385,7 +8385,7 @@
         <v>11</v>
       </c>
       <c r="F280" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G280" t="s" s="0">
         <v>12</v>
@@ -8408,7 +8408,7 @@
         <v>11</v>
       </c>
       <c r="F281" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G281" t="s" s="0">
         <v>12</v>
@@ -8454,7 +8454,7 @@
         <v>11</v>
       </c>
       <c r="F283" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="G283" t="s" s="0">
         <v>12</v>
@@ -8477,7 +8477,7 @@
         <v>11</v>
       </c>
       <c r="F284" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G284" t="s" s="0">
         <v>12</v>
@@ -8523,7 +8523,7 @@
         <v>11</v>
       </c>
       <c r="F286" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G286" t="s" s="0">
         <v>12</v>
@@ -8546,7 +8546,7 @@
         <v>11</v>
       </c>
       <c r="F287" t="n" s="0">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G287" t="s" s="0">
         <v>12</v>
@@ -8569,7 +8569,7 @@
         <v>11</v>
       </c>
       <c r="F288" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G288" t="s" s="0">
         <v>12</v>
@@ -8592,7 +8592,7 @@
         <v>11</v>
       </c>
       <c r="F289" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G289" t="s" s="0">
         <v>12</v>
@@ -8615,7 +8615,7 @@
         <v>11</v>
       </c>
       <c r="F290" t="n" s="0">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="G290" t="s" s="0">
         <v>12</v>
@@ -8661,7 +8661,7 @@
         <v>11</v>
       </c>
       <c r="F292" t="n" s="0">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G292" t="s" s="0">
         <v>12</v>
@@ -8684,7 +8684,7 @@
         <v>11</v>
       </c>
       <c r="F293" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="G293" t="s" s="0">
         <v>12</v>
@@ -8707,7 +8707,7 @@
         <v>11</v>
       </c>
       <c r="F294" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G294" t="s" s="0">
         <v>12</v>
@@ -8730,7 +8730,7 @@
         <v>11</v>
       </c>
       <c r="F295" t="n" s="0">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G295" t="s" s="0">
         <v>12</v>
@@ -8776,7 +8776,7 @@
         <v>11</v>
       </c>
       <c r="F297" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="G297" t="s" s="0">
         <v>12</v>
@@ -8822,7 +8822,7 @@
         <v>11</v>
       </c>
       <c r="F299" t="n" s="0">
-        <v>18.0</v>
+        <v>32.0</v>
       </c>
       <c r="G299" t="s" s="0">
         <v>12</v>
@@ -8845,7 +8845,7 @@
         <v>11</v>
       </c>
       <c r="F300" t="n" s="0">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G300" t="s" s="0">
         <v>12</v>
@@ -8868,7 +8868,7 @@
         <v>11</v>
       </c>
       <c r="F301" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G301" t="s" s="0">
         <v>12</v>
